--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="482">
   <si>
     <t>_id</t>
   </si>
@@ -1043,6 +1043,39 @@
     <t>210111,220111,230111</t>
   </si>
   <si>
+    <t>天龙链头</t>
+  </si>
+  <si>
+    <t>240003,250003,250003,240004,250004,260004</t>
+  </si>
+  <si>
+    <t>天龙手镯</t>
+  </si>
+  <si>
+    <t>天龙戒指</t>
+  </si>
+  <si>
+    <t>240006,250006,260006</t>
+  </si>
+  <si>
+    <t>天龙腰鞋</t>
+  </si>
+  <si>
+    <t>240007,250007,260007,240008,250008,260008</t>
+  </si>
+  <si>
+    <t>天龙衣服</t>
+  </si>
+  <si>
+    <t>240002,250002,260002</t>
+  </si>
+  <si>
+    <t>天龙武器</t>
+  </si>
+  <si>
+    <t>240001,250001,260001</t>
+  </si>
+  <si>
     <t>治愈</t>
   </si>
   <si>
@@ -1536,6 +1569,12 @@
   </si>
   <si>
     <t>72</t>
+  </si>
+  <si>
+    <t>狮王宝宝</t>
+  </si>
+  <si>
+    <t>73</t>
   </si>
   <si>
     <t>一阶四格</t>
@@ -1829,6 +1868,27 @@
   </si>
   <si>
     <t>40000036</t>
+  </si>
+  <si>
+    <t>随机材料</t>
+  </si>
+  <si>
+    <t>40000001,40000004,40000007,40000010,40000013,40000016</t>
+  </si>
+  <si>
+    <t>40000019,40000022,40000025,40000028,40000031,40000034</t>
+  </si>
+  <si>
+    <t>40000002,40000005,40000008,40000011,40000014,40000017</t>
+  </si>
+  <si>
+    <t>40000020,40000023,40000026,40000029,40000032,40000035</t>
+  </si>
+  <si>
+    <t>40000003,40000006,40000009,40000012,40000015,40000018</t>
+  </si>
+  <si>
+    <t>40000021,40000024,40000027,40000030,40000033,40000036</t>
   </si>
 </sst>
 </file>
@@ -3345,7 +3405,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F77"/>
+  <dimension ref="C3:F83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -4404,6 +4464,90 @@
       </c>
       <c r="F77" s="29" t="s">
         <v>204</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:6">
+      <c r="C78" s="1">
+        <v>20073</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E78" s="1">
+        <v>2</v>
+      </c>
+      <c r="F78" s="29" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:6">
+      <c r="C79" s="1">
+        <v>20074</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E79" s="1">
+        <v>2</v>
+      </c>
+      <c r="F79" s="29" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:6">
+      <c r="C80" s="1">
+        <v>20075</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E80" s="1">
+        <v>2</v>
+      </c>
+      <c r="F80" s="29" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:6">
+      <c r="C81" s="1">
+        <v>20076</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E81" s="1">
+        <v>2</v>
+      </c>
+      <c r="F81" s="29" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:6">
+      <c r="C82" s="1">
+        <v>20077</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E82" s="1">
+        <v>2</v>
+      </c>
+      <c r="F82" s="29" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:6">
+      <c r="C83" s="1">
+        <v>20078</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E83" s="1">
+        <v>2</v>
+      </c>
+      <c r="F83" s="29" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -4480,13 +4624,13 @@
         <v>21001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4494,13 +4638,13 @@
         <v>21002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4508,13 +4652,13 @@
         <v>21003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4522,13 +4666,13 @@
         <v>21004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4536,13 +4680,13 @@
         <v>21005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4550,13 +4694,13 @@
         <v>21006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4564,13 +4708,13 @@
         <v>21007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4578,13 +4722,13 @@
         <v>21008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4592,13 +4736,13 @@
         <v>21009</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4606,13 +4750,13 @@
         <v>21010</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4620,13 +4764,13 @@
         <v>21011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4634,17 +4778,28 @@
         <v>21012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F18" s="16"/>
+      <c r="C18" s="1">
+        <v>21013</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F19" s="16"/>
@@ -4730,7 +4885,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F77"/>
+  <dimension ref="C1:F78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -4794,13 +4949,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -4808,13 +4963,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -4822,13 +4977,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -4836,13 +4991,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -4850,13 +5005,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -4864,13 +5019,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -4878,13 +5033,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -4892,13 +5047,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4906,13 +5061,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -4920,13 +5075,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -4934,13 +5089,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -4948,13 +5103,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -4962,13 +5117,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -4976,13 +5131,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -4990,13 +5145,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -5004,13 +5159,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -5018,13 +5173,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -5032,13 +5187,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -5046,13 +5201,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -5060,13 +5215,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
       <c r="F25" s="30" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -5074,13 +5229,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -5088,13 +5243,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -5102,13 +5257,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -5116,13 +5271,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -5130,13 +5285,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -5144,13 +5299,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -5158,13 +5313,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -5172,13 +5327,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -5186,13 +5341,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -5200,13 +5355,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -5214,13 +5369,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -5228,13 +5383,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -5242,13 +5397,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -5256,13 +5411,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -5270,13 +5425,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -5284,13 +5439,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -5298,13 +5453,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -5312,13 +5467,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
       <c r="F43" s="30" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -5326,13 +5481,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
       <c r="F44" s="30" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -5340,13 +5495,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -5354,13 +5509,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -5368,13 +5523,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -5382,13 +5537,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -5396,13 +5551,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -5410,13 +5565,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -5424,13 +5579,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -5438,13 +5593,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -5452,13 +5607,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -5466,13 +5621,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -5480,13 +5635,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -5494,13 +5649,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -5508,13 +5663,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -5522,13 +5677,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -5536,13 +5691,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -5550,13 +5705,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -5564,13 +5719,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -5578,13 +5733,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
       <c r="F62" s="30" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -5592,13 +5747,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
       <c r="F63" s="30" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -5606,13 +5761,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
       <c r="F64" s="30" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -5620,13 +5775,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
       <c r="F65" s="30" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -5634,13 +5789,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -5648,13 +5803,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -5662,13 +5817,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -5676,13 +5831,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -5690,13 +5845,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -5704,13 +5859,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
       <c r="F71" s="30" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -5718,13 +5873,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
       <c r="F72" s="30" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -5732,13 +5887,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
       <c r="F73" s="30" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -5746,13 +5901,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
       <c r="F74" s="30" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5760,13 +5915,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
       <c r="F75" s="30" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -5774,13 +5929,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
       <c r="F76" s="30" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -5788,13 +5943,27 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
       <c r="F77" s="30" t="s">
-        <v>369</v>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:6">
+      <c r="C78" s="11">
+        <v>180073</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="E78" s="6">
+        <v>18</v>
+      </c>
+      <c r="F78" s="30" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -5876,13 +6045,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -5968,13 +6137,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5982,13 +6151,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5996,13 +6165,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6010,13 +6179,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6024,13 +6193,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6038,13 +6207,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6052,13 +6221,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6066,13 +6235,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -6080,13 +6249,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -6131,7 +6300,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F41"/>
+  <dimension ref="C1:F47"/>
   <sheetFormatPr defaultColWidth="12.25" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.25" style="1" customWidth="1"/>
@@ -6196,13 +6365,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6210,13 +6379,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6224,13 +6393,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6238,13 +6407,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6252,13 +6421,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6266,13 +6435,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6280,13 +6449,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6294,13 +6463,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6308,13 +6477,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -6322,13 +6491,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -6336,13 +6505,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -6350,13 +6519,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -6364,13 +6533,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -6378,13 +6547,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -6392,13 +6561,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -6406,13 +6575,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -6420,13 +6589,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -6434,13 +6603,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6448,13 +6617,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6462,13 +6631,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
       <c r="F25" s="30" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6476,13 +6645,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6490,13 +6659,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6504,13 +6673,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6518,13 +6687,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6532,13 +6701,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6546,13 +6715,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6560,13 +6729,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -6574,13 +6743,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -6588,13 +6757,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -6602,13 +6771,13 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -6616,13 +6785,13 @@
         <v>50031</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -6630,13 +6799,13 @@
         <v>50032</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -6644,13 +6813,13 @@
         <v>50033</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -6658,13 +6827,13 @@
         <v>50034</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -6672,13 +6841,13 @@
         <v>50035</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -6686,13 +6855,97 @@
         <v>50036</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>461</v>
+        <v>474</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:6">
+      <c r="C42" s="1">
+        <v>50037</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E42" s="1">
+        <v>6</v>
+      </c>
+      <c r="F42" s="29" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:6">
+      <c r="C43" s="1">
+        <v>50038</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E43" s="1">
+        <v>6</v>
+      </c>
+      <c r="F43" s="29" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:6">
+      <c r="C44" s="1">
+        <v>50039</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E44" s="1">
+        <v>6</v>
+      </c>
+      <c r="F44" s="29" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:6">
+      <c r="C45" s="1">
+        <v>50040</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E45" s="1">
+        <v>6</v>
+      </c>
+      <c r="F45" s="29" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:6">
+      <c r="C46" s="1">
+        <v>50041</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E46" s="1">
+        <v>6</v>
+      </c>
+      <c r="F46" s="29" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:6">
+      <c r="C47" s="1">
+        <v>50042</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E47" s="1">
+        <v>6</v>
+      </c>
+      <c r="F47" s="29" t="s">
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="483">
   <si>
     <t>_id</t>
   </si>
@@ -1050,6 +1050,9 @@
   </si>
   <si>
     <t>天龙手镯</t>
+  </si>
+  <si>
+    <t>240005,250005,260005</t>
   </si>
   <si>
     <t>天龙戒指</t>
@@ -1901,7 +1904,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1950,6 +1953,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2451,16 +2460,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2469,119 +2475,122 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2624,28 +2633,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2981,412 +2991,412 @@
   <dimension ref="C1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="9" style="18"/>
-    <col min="3" max="3" width="8.75" style="18" customWidth="1"/>
-    <col min="4" max="4" width="17.8333333333333" style="18" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="18" customWidth="1"/>
-    <col min="6" max="6" width="30.75" style="19" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="18"/>
+    <col min="1" max="2" width="9" style="19"/>
+    <col min="3" max="3" width="8.75" style="19" customWidth="1"/>
+    <col min="4" max="4" width="17.8333333333333" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="19" customWidth="1"/>
+    <col min="6" max="6" width="30.75" style="20" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" s="18" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F1" s="19"/>
-    </row>
-    <row r="2" s="18" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F2" s="19"/>
-    </row>
-    <row r="3" s="18" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C3" s="20" t="s">
+    <row r="1" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F1" s="20"/>
+    </row>
+    <row r="2" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F2" s="20"/>
+    </row>
+    <row r="3" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="21" t="s">
+      <c r="E3" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="18" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C4" s="20" t="s">
+    <row r="4" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="18" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C5" s="20" t="s">
+    <row r="5" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="22" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="18" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="18">
+    <row r="6" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="19">
         <v>1</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <v>5</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="26" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
-      <c r="C7" s="18">
-        <v>2</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="C7" s="19">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <v>5</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="26" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <v>3</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <v>5</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="26" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <v>4</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <v>5</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="26" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <v>5</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <v>6</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="27" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <v>6</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <v>6</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <v>7</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <v>6</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="27" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
-      <c r="C13" s="18">
+      <c r="C13" s="19">
         <v>8</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <v>6</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="27" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
-      <c r="C14" s="18">
+      <c r="C14" s="19">
         <v>9</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <v>6</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="27" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
-      <c r="C15" s="18">
+      <c r="C15" s="19">
         <v>10</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <v>6</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="27" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
-      <c r="C16" s="18">
+      <c r="C16" s="19">
         <v>11</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="19">
         <v>5</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="20" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="18">
+      <c r="C17" s="19">
         <v>12</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="19">
         <v>5</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="20" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="18">
+      <c r="C18" s="19">
         <v>13</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="19">
         <v>5</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="18">
+      <c r="C19" s="19">
         <v>14</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="19">
         <v>5</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="20" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <v>15</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="19">
         <v>5</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="20" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
-      <c r="C21" s="18">
+      <c r="C21" s="19">
         <v>16</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="19">
         <v>5</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="20" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" s="18" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C22" s="23"/>
+    <row r="22" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C22" s="24"/>
     </row>
     <row r="26" customHeight="1" spans="3:6">
-      <c r="C26" s="18">
+      <c r="C26" s="19">
         <v>21</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="19">
         <v>5</v>
       </c>
-      <c r="F26" s="27" t="s">
+      <c r="F26" s="28" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
-      <c r="C27" s="18">
+      <c r="C27" s="19">
         <v>22</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="19">
         <v>5</v>
       </c>
-      <c r="F27" s="27" t="s">
+      <c r="F27" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
-      <c r="C28" s="18">
+      <c r="C28" s="19">
         <v>23</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="19">
         <v>5</v>
       </c>
-      <c r="F28" s="27" t="s">
+      <c r="F28" s="28" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
-      <c r="C29" s="18">
+      <c r="C29" s="19">
         <v>24</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="19">
         <v>5</v>
       </c>
-      <c r="F29" s="27" t="s">
+      <c r="F29" s="28" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
-      <c r="C30" s="18">
+      <c r="C30" s="19">
         <v>25</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="19">
         <v>5</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
-      <c r="C31" s="18">
+      <c r="C31" s="19">
         <v>26</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="19">
         <v>5</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="28" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
-      <c r="C32" s="18">
+      <c r="C32" s="19">
         <v>27</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="19">
         <v>5</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="28" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
-      <c r="C33" s="18">
+      <c r="C33" s="19">
         <v>28</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="19">
         <v>5</v>
       </c>
-      <c r="F33" s="27" t="s">
+      <c r="F33" s="28" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
-      <c r="C34" s="18">
+      <c r="C34" s="19">
         <v>29</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="19">
         <v>5</v>
       </c>
-      <c r="F34" s="26" t="s">
+      <c r="F34" s="27" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3405,7 +3415,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F83"/>
+  <dimension ref="C3:F89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -3468,7 +3478,7 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="29" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3482,7 +3492,7 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="29" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3496,7 +3506,7 @@
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="29" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3510,7 +3520,7 @@
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="29" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3524,7 +3534,7 @@
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="29" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3538,7 +3548,7 @@
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="30" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3552,7 +3562,7 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="29" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3566,7 +3576,7 @@
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="29" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3580,7 +3590,7 @@
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="29" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3594,7 +3604,7 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="29" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3608,7 +3618,7 @@
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="28" t="s">
+      <c r="F16" s="29" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3622,7 +3632,7 @@
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="30" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3636,7 +3646,7 @@
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="29" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3650,7 +3660,7 @@
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="29" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3664,7 +3674,7 @@
       <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="29" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3678,7 +3688,7 @@
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="29" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3692,7 +3702,7 @@
       <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="29" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3706,7 +3716,7 @@
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="30" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3720,7 +3730,7 @@
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="29" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3734,7 +3744,7 @@
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="29" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3748,7 +3758,7 @@
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="29" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3762,7 +3772,7 @@
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="29" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3776,7 +3786,7 @@
       <c r="E28" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3790,7 +3800,7 @@
       <c r="E29" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="29" t="s">
+      <c r="F29" s="30" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3804,7 +3814,7 @@
       <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="29" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3818,7 +3828,7 @@
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="29" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3832,7 +3842,7 @@
       <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="29" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3846,7 +3856,7 @@
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="29" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3860,7 +3870,7 @@
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="F34" s="29" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3874,7 +3884,7 @@
       <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="F35" s="29" t="s">
+      <c r="F35" s="30" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3888,7 +3898,7 @@
       <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="28" t="s">
+      <c r="F36" s="29" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3902,7 +3912,7 @@
       <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="28" t="s">
+      <c r="F37" s="29" t="s">
         <v>124</v>
       </c>
     </row>
@@ -3916,7 +3926,7 @@
       <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="28" t="s">
+      <c r="F38" s="29" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3930,7 +3940,7 @@
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="28" t="s">
+      <c r="F39" s="29" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3944,7 +3954,7 @@
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="29" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3958,7 +3968,7 @@
       <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="29" t="s">
+      <c r="F41" s="30" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3972,7 +3982,7 @@
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="29" t="s">
         <v>134</v>
       </c>
     </row>
@@ -3986,7 +3996,7 @@
       <c r="E43" s="1">
         <v>2</v>
       </c>
-      <c r="F43" s="28" t="s">
+      <c r="F43" s="29" t="s">
         <v>136</v>
       </c>
     </row>
@@ -4000,7 +4010,7 @@
       <c r="E44" s="1">
         <v>2</v>
       </c>
-      <c r="F44" s="28" t="s">
+      <c r="F44" s="29" t="s">
         <v>138</v>
       </c>
     </row>
@@ -4014,7 +4024,7 @@
       <c r="E45" s="1">
         <v>2</v>
       </c>
-      <c r="F45" s="28" t="s">
+      <c r="F45" s="29" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4028,7 +4038,7 @@
       <c r="E46" s="1">
         <v>2</v>
       </c>
-      <c r="F46" s="28" t="s">
+      <c r="F46" s="29" t="s">
         <v>142</v>
       </c>
     </row>
@@ -4042,7 +4052,7 @@
       <c r="E47" s="1">
         <v>2</v>
       </c>
-      <c r="F47" s="29" t="s">
+      <c r="F47" s="30" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4056,7 +4066,7 @@
       <c r="E48" s="1">
         <v>2</v>
       </c>
-      <c r="F48" s="29" t="s">
+      <c r="F48" s="30" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4070,7 +4080,7 @@
       <c r="E49" s="1">
         <v>2</v>
       </c>
-      <c r="F49" s="29" t="s">
+      <c r="F49" s="30" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4084,7 +4094,7 @@
       <c r="E50" s="1">
         <v>2</v>
       </c>
-      <c r="F50" s="29" t="s">
+      <c r="F50" s="30" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4098,7 +4108,7 @@
       <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="29" t="s">
+      <c r="F51" s="30" t="s">
         <v>152</v>
       </c>
     </row>
@@ -4112,7 +4122,7 @@
       <c r="E52" s="1">
         <v>2</v>
       </c>
-      <c r="F52" s="29" t="s">
+      <c r="F52" s="30" t="s">
         <v>154</v>
       </c>
     </row>
@@ -4126,7 +4136,7 @@
       <c r="E53" s="1">
         <v>2</v>
       </c>
-      <c r="F53" s="29" t="s">
+      <c r="F53" s="30" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4140,7 +4150,7 @@
       <c r="E54" s="1">
         <v>2</v>
       </c>
-      <c r="F54" s="29" t="s">
+      <c r="F54" s="30" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4154,7 +4164,7 @@
       <c r="E55" s="1">
         <v>2</v>
       </c>
-      <c r="F55" s="29" t="s">
+      <c r="F55" s="30" t="s">
         <v>160</v>
       </c>
     </row>
@@ -4168,7 +4178,7 @@
       <c r="E56" s="1">
         <v>2</v>
       </c>
-      <c r="F56" s="29" t="s">
+      <c r="F56" s="30" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4182,7 +4192,7 @@
       <c r="E57" s="1">
         <v>2</v>
       </c>
-      <c r="F57" s="29" t="s">
+      <c r="F57" s="30" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4196,7 +4206,7 @@
       <c r="E58" s="1">
         <v>2</v>
       </c>
-      <c r="F58" s="29" t="s">
+      <c r="F58" s="30" t="s">
         <v>166</v>
       </c>
     </row>
@@ -4210,7 +4220,7 @@
       <c r="E59" s="1">
         <v>2</v>
       </c>
-      <c r="F59" s="29" t="s">
+      <c r="F59" s="30" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4224,7 +4234,7 @@
       <c r="E60" s="1">
         <v>2</v>
       </c>
-      <c r="F60" s="29" t="s">
+      <c r="F60" s="30" t="s">
         <v>170</v>
       </c>
     </row>
@@ -4238,7 +4248,7 @@
       <c r="E61" s="1">
         <v>2</v>
       </c>
-      <c r="F61" s="29" t="s">
+      <c r="F61" s="30" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4252,7 +4262,7 @@
       <c r="E62" s="1">
         <v>2</v>
       </c>
-      <c r="F62" s="29" t="s">
+      <c r="F62" s="30" t="s">
         <v>174</v>
       </c>
     </row>
@@ -4266,7 +4276,7 @@
       <c r="E63" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="29" t="s">
+      <c r="F63" s="30" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4280,7 +4290,7 @@
       <c r="E64" s="1">
         <v>2</v>
       </c>
-      <c r="F64" s="29" t="s">
+      <c r="F64" s="30" t="s">
         <v>178</v>
       </c>
     </row>
@@ -4294,7 +4304,7 @@
       <c r="E65" s="1">
         <v>2</v>
       </c>
-      <c r="F65" s="29" t="s">
+      <c r="F65" s="30" t="s">
         <v>180</v>
       </c>
     </row>
@@ -4308,7 +4318,7 @@
       <c r="E66" s="1">
         <v>2</v>
       </c>
-      <c r="F66" s="29" t="s">
+      <c r="F66" s="30" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4322,7 +4332,7 @@
       <c r="E67" s="1">
         <v>2</v>
       </c>
-      <c r="F67" s="29" t="s">
+      <c r="F67" s="30" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4336,7 +4346,7 @@
       <c r="E68" s="1">
         <v>2</v>
       </c>
-      <c r="F68" s="29" t="s">
+      <c r="F68" s="30" t="s">
         <v>186</v>
       </c>
     </row>
@@ -4350,7 +4360,7 @@
       <c r="E69" s="1">
         <v>2</v>
       </c>
-      <c r="F69" s="29" t="s">
+      <c r="F69" s="30" t="s">
         <v>188</v>
       </c>
     </row>
@@ -4364,7 +4374,7 @@
       <c r="E70" s="1">
         <v>2</v>
       </c>
-      <c r="F70" s="29" t="s">
+      <c r="F70" s="30" t="s">
         <v>190</v>
       </c>
     </row>
@@ -4378,7 +4388,7 @@
       <c r="E71" s="1">
         <v>2</v>
       </c>
-      <c r="F71" s="29" t="s">
+      <c r="F71" s="30" t="s">
         <v>192</v>
       </c>
     </row>
@@ -4392,7 +4402,7 @@
       <c r="E72" s="1">
         <v>2</v>
       </c>
-      <c r="F72" s="29" t="s">
+      <c r="F72" s="30" t="s">
         <v>194</v>
       </c>
     </row>
@@ -4406,7 +4416,7 @@
       <c r="E73" s="1">
         <v>2</v>
       </c>
-      <c r="F73" s="29" t="s">
+      <c r="F73" s="30" t="s">
         <v>196</v>
       </c>
     </row>
@@ -4420,7 +4430,7 @@
       <c r="E74" s="1">
         <v>2</v>
       </c>
-      <c r="F74" s="29" t="s">
+      <c r="F74" s="30" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4434,7 +4444,7 @@
       <c r="E75" s="1">
         <v>2</v>
       </c>
-      <c r="F75" s="29" t="s">
+      <c r="F75" s="30" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4448,7 +4458,7 @@
       <c r="E76" s="1">
         <v>2</v>
       </c>
-      <c r="F76" s="29" t="s">
+      <c r="F76" s="30" t="s">
         <v>202</v>
       </c>
     </row>
@@ -4462,7 +4472,7 @@
       <c r="E77" s="1">
         <v>2</v>
       </c>
-      <c r="F77" s="29" t="s">
+      <c r="F77" s="30" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4476,7 +4486,7 @@
       <c r="E78" s="1">
         <v>2</v>
       </c>
-      <c r="F78" s="29" t="s">
+      <c r="F78" s="30" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4490,8 +4500,8 @@
       <c r="E79" s="1">
         <v>2</v>
       </c>
-      <c r="F79" s="29" t="s">
-        <v>196</v>
+      <c r="F79" s="30" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:6">
@@ -4499,13 +4509,13 @@
         <v>20075</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
       </c>
-      <c r="F80" s="29" t="s">
-        <v>209</v>
+      <c r="F80" s="30" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:6">
@@ -4513,13 +4523,13 @@
         <v>20076</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
       </c>
-      <c r="F81" s="29" t="s">
-        <v>211</v>
+      <c r="F81" s="30" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:6">
@@ -4527,13 +4537,13 @@
         <v>20077</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
       </c>
-      <c r="F82" s="29" t="s">
-        <v>213</v>
+      <c r="F82" s="30" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:6">
@@ -4541,14 +4551,17 @@
         <v>20078</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
       </c>
-      <c r="F83" s="29" t="s">
-        <v>215</v>
-      </c>
+      <c r="F83" s="30" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:6">
+      <c r="F89" s="18"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4624,13 +4637,13 @@
         <v>21001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="28" t="s">
-        <v>217</v>
+      <c r="F6" s="29" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4638,13 +4651,13 @@
         <v>21002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="28" t="s">
-        <v>219</v>
+      <c r="F7" s="29" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4652,13 +4665,13 @@
         <v>21003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="28" t="s">
-        <v>221</v>
+      <c r="F8" s="29" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4666,13 +4679,13 @@
         <v>21004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="28" t="s">
-        <v>223</v>
+      <c r="F9" s="29" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4680,13 +4693,13 @@
         <v>21005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="28" t="s">
-        <v>225</v>
+      <c r="F10" s="29" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4694,13 +4707,13 @@
         <v>21006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="28" t="s">
-        <v>227</v>
+      <c r="F11" s="29" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4708,13 +4721,13 @@
         <v>21007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="28" t="s">
-        <v>229</v>
+      <c r="F12" s="29" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4722,13 +4735,13 @@
         <v>21008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="28" t="s">
-        <v>231</v>
+      <c r="F13" s="29" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4736,13 +4749,13 @@
         <v>21009</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="28" t="s">
-        <v>233</v>
+      <c r="F14" s="29" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4750,13 +4763,13 @@
         <v>21010</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="28" t="s">
-        <v>235</v>
+      <c r="F15" s="29" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4764,13 +4777,13 @@
         <v>21011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="28" t="s">
-        <v>237</v>
+      <c r="F16" s="29" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4778,13 +4791,13 @@
         <v>21012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>239</v>
+      <c r="F17" s="29" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4792,13 +4805,13 @@
         <v>21013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="28" t="s">
-        <v>239</v>
+      <c r="F18" s="29" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4949,13 +4962,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
-      <c r="F6" s="30" t="s">
-        <v>241</v>
+      <c r="F6" s="31" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -4963,13 +4976,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
-      <c r="F7" s="30" t="s">
-        <v>243</v>
+      <c r="F7" s="31" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -4977,13 +4990,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
-      <c r="F8" s="30" t="s">
-        <v>245</v>
+      <c r="F8" s="31" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -4991,13 +5004,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
-      <c r="F9" s="30" t="s">
-        <v>247</v>
+      <c r="F9" s="31" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -5005,13 +5018,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
-      <c r="F10" s="30" t="s">
-        <v>249</v>
+      <c r="F10" s="31" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -5019,13 +5032,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
-      <c r="F11" s="30" t="s">
-        <v>251</v>
+      <c r="F11" s="31" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -5033,13 +5046,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>253</v>
+      <c r="F12" s="31" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -5047,13 +5060,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
-      <c r="F13" s="30" t="s">
-        <v>255</v>
+      <c r="F13" s="31" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -5061,13 +5074,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
-      <c r="F14" s="30" t="s">
-        <v>257</v>
+      <c r="F14" s="31" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -5075,13 +5088,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
-      <c r="F15" s="30" t="s">
-        <v>259</v>
+      <c r="F15" s="31" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -5089,13 +5102,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
-      <c r="F16" s="30" t="s">
-        <v>261</v>
+      <c r="F16" s="31" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -5103,13 +5116,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
-      <c r="F17" s="30" t="s">
-        <v>263</v>
+      <c r="F17" s="31" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -5117,13 +5130,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
-      <c r="F18" s="30" t="s">
-        <v>265</v>
+      <c r="F18" s="31" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -5131,13 +5144,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
-      <c r="F19" s="30" t="s">
-        <v>267</v>
+      <c r="F19" s="31" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -5145,13 +5158,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
-      <c r="F20" s="30" t="s">
-        <v>269</v>
+      <c r="F20" s="31" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -5159,13 +5172,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
-      <c r="F21" s="30" t="s">
-        <v>271</v>
+      <c r="F21" s="31" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -5173,13 +5186,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
-      <c r="F22" s="30" t="s">
-        <v>273</v>
+      <c r="F22" s="31" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -5187,13 +5200,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
-      <c r="F23" s="30" t="s">
-        <v>275</v>
+      <c r="F23" s="31" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -5201,13 +5214,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
-      <c r="F24" s="30" t="s">
-        <v>277</v>
+      <c r="F24" s="31" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -5215,13 +5228,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
-      <c r="F25" s="30" t="s">
-        <v>279</v>
+      <c r="F25" s="31" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -5229,13 +5242,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
-      <c r="F26" s="30" t="s">
-        <v>281</v>
+      <c r="F26" s="31" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -5243,13 +5256,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
-      <c r="F27" s="30" t="s">
-        <v>283</v>
+      <c r="F27" s="31" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -5257,13 +5270,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
-      <c r="F28" s="30" t="s">
-        <v>285</v>
+      <c r="F28" s="31" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -5271,13 +5284,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
-      <c r="F29" s="30" t="s">
-        <v>287</v>
+      <c r="F29" s="31" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -5285,13 +5298,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
-      <c r="F30" s="30" t="s">
-        <v>289</v>
+      <c r="F30" s="31" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -5299,13 +5312,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
-      <c r="F31" s="30" t="s">
-        <v>291</v>
+      <c r="F31" s="31" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -5313,13 +5326,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
-      <c r="F32" s="30" t="s">
-        <v>293</v>
+      <c r="F32" s="31" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -5327,13 +5340,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
-      <c r="F33" s="30" t="s">
-        <v>295</v>
+      <c r="F33" s="31" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -5341,13 +5354,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
-      <c r="F34" s="30" t="s">
-        <v>297</v>
+      <c r="F34" s="31" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -5355,13 +5368,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
-      <c r="F35" s="30" t="s">
-        <v>299</v>
+      <c r="F35" s="31" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -5369,13 +5382,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
-      <c r="F36" s="30" t="s">
-        <v>301</v>
+      <c r="F36" s="31" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -5383,13 +5396,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
-      <c r="F37" s="30" t="s">
-        <v>303</v>
+      <c r="F37" s="31" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -5397,13 +5410,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
-      <c r="F38" s="30" t="s">
-        <v>305</v>
+      <c r="F38" s="31" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -5411,13 +5424,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
-      <c r="F39" s="30" t="s">
-        <v>307</v>
+      <c r="F39" s="31" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -5425,13 +5438,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
-      <c r="F40" s="30" t="s">
-        <v>309</v>
+      <c r="F40" s="31" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -5439,13 +5452,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
-      <c r="F41" s="30" t="s">
-        <v>311</v>
+      <c r="F41" s="31" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -5453,13 +5466,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
-      <c r="F42" s="30" t="s">
-        <v>313</v>
+      <c r="F42" s="31" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -5467,13 +5480,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
-      <c r="F43" s="30" t="s">
-        <v>315</v>
+      <c r="F43" s="31" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -5481,13 +5494,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
-      <c r="F44" s="30" t="s">
-        <v>317</v>
+      <c r="F44" s="31" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -5495,13 +5508,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
-      <c r="F45" s="30" t="s">
-        <v>319</v>
+      <c r="F45" s="31" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -5509,13 +5522,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
-      <c r="F46" s="30" t="s">
-        <v>321</v>
+      <c r="F46" s="31" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -5523,13 +5536,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
-      <c r="F47" s="30" t="s">
-        <v>323</v>
+      <c r="F47" s="31" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -5537,13 +5550,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
-      <c r="F48" s="30" t="s">
-        <v>325</v>
+      <c r="F48" s="31" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -5551,13 +5564,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
-      <c r="F49" s="30" t="s">
-        <v>327</v>
+      <c r="F49" s="31" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -5565,13 +5578,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
-      <c r="F50" s="30" t="s">
-        <v>329</v>
+      <c r="F50" s="31" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -5579,13 +5592,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
-      <c r="F51" s="30" t="s">
-        <v>331</v>
+      <c r="F51" s="31" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -5593,13 +5606,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
-      <c r="F52" s="30" t="s">
-        <v>333</v>
+      <c r="F52" s="31" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -5607,13 +5620,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
-      <c r="F53" s="30" t="s">
-        <v>334</v>
+      <c r="F53" s="31" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -5621,13 +5634,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
-      <c r="F54" s="30" t="s">
-        <v>336</v>
+      <c r="F54" s="31" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -5635,13 +5648,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
-      <c r="F55" s="30" t="s">
-        <v>338</v>
+      <c r="F55" s="31" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -5649,13 +5662,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
-      <c r="F56" s="30" t="s">
-        <v>340</v>
+      <c r="F56" s="31" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -5663,13 +5676,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
-      <c r="F57" s="30" t="s">
-        <v>342</v>
+      <c r="F57" s="31" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -5677,13 +5690,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
-      <c r="F58" s="30" t="s">
-        <v>344</v>
+      <c r="F58" s="31" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -5691,13 +5704,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
-      <c r="F59" s="30" t="s">
-        <v>346</v>
+      <c r="F59" s="31" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -5705,13 +5718,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
-      <c r="F60" s="30" t="s">
-        <v>348</v>
+      <c r="F60" s="31" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -5719,13 +5732,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
-      <c r="F61" s="30" t="s">
-        <v>350</v>
+      <c r="F61" s="31" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -5733,13 +5746,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
-      <c r="F62" s="30" t="s">
-        <v>351</v>
+      <c r="F62" s="31" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -5747,13 +5760,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
-      <c r="F63" s="30" t="s">
-        <v>353</v>
+      <c r="F63" s="31" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -5761,13 +5774,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
-      <c r="F64" s="30" t="s">
-        <v>355</v>
+      <c r="F64" s="31" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -5775,13 +5788,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
-      <c r="F65" s="30" t="s">
-        <v>357</v>
+      <c r="F65" s="31" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -5789,13 +5802,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
-      <c r="F66" s="30" t="s">
-        <v>359</v>
+      <c r="F66" s="31" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -5803,13 +5816,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
-      <c r="F67" s="30" t="s">
-        <v>361</v>
+      <c r="F67" s="31" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -5817,13 +5830,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
-      <c r="F68" s="30" t="s">
-        <v>363</v>
+      <c r="F68" s="31" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -5831,13 +5844,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
-      <c r="F69" s="30" t="s">
-        <v>365</v>
+      <c r="F69" s="31" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -5845,13 +5858,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
-      <c r="F70" s="30" t="s">
-        <v>367</v>
+      <c r="F70" s="31" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -5859,13 +5872,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
-      <c r="F71" s="30" t="s">
-        <v>369</v>
+      <c r="F71" s="31" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -5873,13 +5886,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
-      <c r="F72" s="30" t="s">
-        <v>370</v>
+      <c r="F72" s="31" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -5887,13 +5900,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
-      <c r="F73" s="30" t="s">
-        <v>372</v>
+      <c r="F73" s="31" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -5901,13 +5914,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
-      <c r="F74" s="30" t="s">
-        <v>374</v>
+      <c r="F74" s="31" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5915,13 +5928,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
-      <c r="F75" s="30" t="s">
-        <v>376</v>
+      <c r="F75" s="31" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -5929,13 +5942,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
-      <c r="F76" s="30" t="s">
-        <v>378</v>
+      <c r="F76" s="31" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -5943,13 +5956,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
-      <c r="F77" s="30" t="s">
-        <v>380</v>
+      <c r="F77" s="31" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:6">
@@ -5957,13 +5970,13 @@
         <v>180073</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E78" s="6">
         <v>18</v>
       </c>
-      <c r="F78" s="30" t="s">
-        <v>382</v>
+      <c r="F78" s="31" t="s">
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -6045,13 +6058,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -6137,13 +6150,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="31" t="s">
-        <v>386</v>
+      <c r="F6" s="32" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6151,13 +6164,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="31" t="s">
-        <v>388</v>
+      <c r="F7" s="32" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6165,13 +6178,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>390</v>
+      <c r="F8" s="32" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6179,13 +6192,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="31" t="s">
-        <v>392</v>
+      <c r="F9" s="32" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6193,13 +6206,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
-      <c r="F10" s="31" t="s">
-        <v>394</v>
+      <c r="F10" s="32" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6207,13 +6220,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="31" t="s">
-        <v>396</v>
+      <c r="F11" s="32" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6221,13 +6234,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>398</v>
+      <c r="F12" s="32" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6235,13 +6248,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
-      <c r="F13" s="32" t="s">
-        <v>400</v>
+      <c r="F13" s="33" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -6249,13 +6262,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
-      <c r="F14" s="32" t="s">
-        <v>402</v>
+      <c r="F14" s="33" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -6365,13 +6378,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
-      <c r="F6" s="30" t="s">
-        <v>404</v>
+      <c r="F6" s="31" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6379,13 +6392,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
-      <c r="F7" s="30" t="s">
-        <v>406</v>
+      <c r="F7" s="31" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6393,13 +6406,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
-      <c r="F8" s="30" t="s">
-        <v>408</v>
+      <c r="F8" s="31" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6407,13 +6420,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
-      <c r="F9" s="30" t="s">
-        <v>410</v>
+      <c r="F9" s="31" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6421,13 +6434,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
-      <c r="F10" s="30" t="s">
-        <v>412</v>
+      <c r="F10" s="31" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6435,13 +6448,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="30" t="s">
-        <v>414</v>
+      <c r="F11" s="31" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6449,13 +6462,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>416</v>
+      <c r="F12" s="31" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6463,13 +6476,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
-      <c r="F13" s="30" t="s">
-        <v>418</v>
+      <c r="F13" s="31" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6477,13 +6490,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
-      <c r="F14" s="30" t="s">
-        <v>420</v>
+      <c r="F14" s="31" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -6491,13 +6504,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
-      <c r="F15" s="30" t="s">
-        <v>422</v>
+      <c r="F15" s="31" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -6505,13 +6518,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
-      <c r="F16" s="30" t="s">
-        <v>424</v>
+      <c r="F16" s="31" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -6519,13 +6532,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
-      <c r="F17" s="30" t="s">
-        <v>426</v>
+      <c r="F17" s="31" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -6533,13 +6546,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
-      <c r="F18" s="30" t="s">
-        <v>428</v>
+      <c r="F18" s="31" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -6547,13 +6560,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
-      <c r="F19" s="30" t="s">
-        <v>430</v>
+      <c r="F19" s="31" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -6561,13 +6574,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
-      <c r="F20" s="30" t="s">
-        <v>432</v>
+      <c r="F20" s="31" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -6575,13 +6588,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
-      <c r="F21" s="30" t="s">
-        <v>434</v>
+      <c r="F21" s="31" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -6589,13 +6602,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
-      <c r="F22" s="30" t="s">
-        <v>436</v>
+      <c r="F22" s="31" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -6603,13 +6616,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
-      <c r="F23" s="30" t="s">
-        <v>438</v>
+      <c r="F23" s="31" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6617,13 +6630,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
-      <c r="F24" s="30" t="s">
-        <v>440</v>
+      <c r="F24" s="31" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6631,13 +6644,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
-      <c r="F25" s="30" t="s">
-        <v>442</v>
+      <c r="F25" s="31" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6645,13 +6658,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
-      <c r="F26" s="30" t="s">
-        <v>444</v>
+      <c r="F26" s="31" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6659,13 +6672,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
-      <c r="F27" s="30" t="s">
-        <v>446</v>
+      <c r="F27" s="31" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6673,13 +6686,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
-      <c r="F28" s="30" t="s">
-        <v>448</v>
+      <c r="F28" s="31" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6687,13 +6700,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
-      <c r="F29" s="30" t="s">
-        <v>450</v>
+      <c r="F29" s="31" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6701,13 +6714,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
-      <c r="F30" s="30" t="s">
-        <v>452</v>
+      <c r="F30" s="31" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6715,13 +6728,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
-      <c r="F31" s="30" t="s">
-        <v>454</v>
+      <c r="F31" s="31" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6729,13 +6742,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
-      <c r="F32" s="30" t="s">
-        <v>456</v>
+      <c r="F32" s="31" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -6743,13 +6756,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
-      <c r="F33" s="30" t="s">
-        <v>458</v>
+      <c r="F33" s="31" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -6757,13 +6770,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
-      <c r="F34" s="30" t="s">
-        <v>460</v>
+      <c r="F34" s="31" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -6771,13 +6784,13 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
-      <c r="F35" s="30" t="s">
-        <v>462</v>
+      <c r="F35" s="31" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -6785,13 +6798,13 @@
         <v>50031</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
       </c>
-      <c r="F36" s="30" t="s">
-        <v>464</v>
+      <c r="F36" s="31" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -6799,13 +6812,13 @@
         <v>50032</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
       </c>
-      <c r="F37" s="30" t="s">
-        <v>466</v>
+      <c r="F37" s="31" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -6813,13 +6826,13 @@
         <v>50033</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
       </c>
-      <c r="F38" s="30" t="s">
-        <v>468</v>
+      <c r="F38" s="31" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -6827,13 +6840,13 @@
         <v>50034</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
       </c>
-      <c r="F39" s="30" t="s">
-        <v>470</v>
+      <c r="F39" s="31" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -6841,13 +6854,13 @@
         <v>50035</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
       </c>
-      <c r="F40" s="30" t="s">
-        <v>472</v>
+      <c r="F40" s="31" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -6855,13 +6868,13 @@
         <v>50036</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
       </c>
-      <c r="F41" s="30" t="s">
-        <v>474</v>
+      <c r="F41" s="31" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -6869,13 +6882,13 @@
         <v>50037</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E42" s="1">
         <v>6</v>
       </c>
-      <c r="F42" s="29" t="s">
-        <v>476</v>
+      <c r="F42" s="30" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -6883,13 +6896,13 @@
         <v>50038</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E43" s="1">
         <v>6</v>
       </c>
-      <c r="F43" s="29" t="s">
-        <v>477</v>
+      <c r="F43" s="30" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -6897,13 +6910,13 @@
         <v>50039</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E44" s="1">
         <v>6</v>
       </c>
-      <c r="F44" s="29" t="s">
-        <v>478</v>
+      <c r="F44" s="30" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -6911,13 +6924,13 @@
         <v>50040</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E45" s="1">
         <v>6</v>
       </c>
-      <c r="F45" s="29" t="s">
-        <v>479</v>
+      <c r="F45" s="30" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -6925,13 +6938,13 @@
         <v>50041</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E46" s="1">
         <v>6</v>
       </c>
-      <c r="F46" s="29" t="s">
-        <v>480</v>
+      <c r="F46" s="30" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -6939,13 +6952,13 @@
         <v>50042</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E47" s="1">
         <v>6</v>
       </c>
-      <c r="F47" s="29" t="s">
-        <v>481</v>
+      <c r="F47" s="30" t="s">
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -1046,7 +1046,7 @@
     <t>天龙链头</t>
   </si>
   <si>
-    <t>240003,250003,250003,240004,250004,260004</t>
+    <t>240003,250003,260003,240004,250004,260004</t>
   </si>
   <si>
     <t>天龙手镯</t>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="489">
   <si>
     <t>_id</t>
   </si>
@@ -1149,6 +1149,24 @@
   </si>
   <si>
     <t>201034,201035,201036</t>
+  </si>
+  <si>
+    <t>不灭</t>
+  </si>
+  <si>
+    <t>201037,201038,201039</t>
+  </si>
+  <si>
+    <t>镇岳</t>
+  </si>
+  <si>
+    <t>201040,201041,201042</t>
+  </si>
+  <si>
+    <t>冰霜</t>
+  </si>
+  <si>
+    <t>201043,201044,201045</t>
   </si>
   <si>
     <t>狼宝宝</t>
@@ -2590,7 +2608,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2629,6 +2647,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2991,412 +3012,412 @@
   <dimension ref="C1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="9" style="19"/>
-    <col min="3" max="3" width="8.75" style="19" customWidth="1"/>
-    <col min="4" max="4" width="17.8333333333333" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="19" customWidth="1"/>
-    <col min="6" max="6" width="30.75" style="20" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="19"/>
+    <col min="1" max="2" width="9" style="20"/>
+    <col min="3" max="3" width="8.75" style="20" customWidth="1"/>
+    <col min="4" max="4" width="17.8333333333333" style="20" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="20" customWidth="1"/>
+    <col min="6" max="6" width="30.75" style="21" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" s="19" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F1" s="20"/>
-    </row>
-    <row r="2" s="19" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F2" s="20"/>
-    </row>
-    <row r="3" s="19" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C3" s="21" t="s">
+    <row r="1" s="20" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" s="20" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" s="20" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="22" t="s">
+      <c r="E3" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="23" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="19" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C4" s="21" t="s">
+    <row r="4" s="20" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="19" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C5" s="21" t="s">
+    <row r="5" s="20" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C5" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="23" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="19" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="19">
+    <row r="6" s="20" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="20">
         <v>1</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>5</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="27" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
-      <c r="C7" s="19">
-        <v>2</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="C7" s="20">
+        <v>2</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <v>5</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="27" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <v>3</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <v>5</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="27" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <v>4</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <v>5</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="27" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <v>5</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <v>6</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="28" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <v>6</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <v>6</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <v>7</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <v>6</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="28" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <v>8</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <v>6</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <v>9</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <v>6</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="28" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <v>10</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <v>6</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="28" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <v>11</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <v>5</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="21" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="19">
+      <c r="C17" s="20">
         <v>12</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <v>5</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <v>13</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <v>5</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="21" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="19">
+      <c r="C19" s="20">
         <v>14</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <v>5</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <v>15</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <v>5</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="21" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <v>16</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <v>5</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="21" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" s="19" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C22" s="24"/>
+    <row r="22" s="20" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C22" s="25"/>
     </row>
     <row r="26" customHeight="1" spans="3:6">
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <v>21</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <v>5</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="29" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <v>22</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <v>5</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="29" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <v>23</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <v>5</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
-      <c r="C29" s="19">
+      <c r="C29" s="20">
         <v>24</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="20">
         <v>5</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="29" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
-      <c r="C30" s="19">
+      <c r="C30" s="20">
         <v>25</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="20">
         <v>5</v>
       </c>
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="29" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
-      <c r="C31" s="19">
+      <c r="C31" s="20">
         <v>26</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="20">
         <v>5</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="29" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
-      <c r="C32" s="19">
+      <c r="C32" s="20">
         <v>27</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="20">
         <v>5</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="29" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
-      <c r="C33" s="19">
+      <c r="C33" s="20">
         <v>28</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="20">
         <v>5</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="29" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
-      <c r="C34" s="19">
+      <c r="C34" s="20">
         <v>29</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="20">
         <v>5</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="28" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3478,7 +3499,7 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="30" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3492,7 +3513,7 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="30" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3506,7 +3527,7 @@
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="30" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3520,7 +3541,7 @@
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="30" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3534,7 +3555,7 @@
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="30" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3548,7 +3569,7 @@
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="31" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3562,7 +3583,7 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="30" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3576,7 +3597,7 @@
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="30" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3590,7 +3611,7 @@
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="30" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3604,7 +3625,7 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="30" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3618,7 +3639,7 @@
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="30" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3632,7 +3653,7 @@
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="31" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3646,7 +3667,7 @@
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F18" s="30" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3660,7 +3681,7 @@
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="30" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3674,7 +3695,7 @@
       <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="30" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3688,7 +3709,7 @@
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="30" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3702,7 +3723,7 @@
       <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="30" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3716,7 +3737,7 @@
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="30" t="s">
+      <c r="F23" s="31" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3730,7 +3751,7 @@
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="30" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3744,7 +3765,7 @@
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="30" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3758,7 +3779,7 @@
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="29" t="s">
+      <c r="F26" s="30" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3772,7 +3793,7 @@
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="30" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3786,7 +3807,7 @@
       <c r="E28" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="30" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3800,7 +3821,7 @@
       <c r="E29" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="30" t="s">
+      <c r="F29" s="31" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3814,7 +3835,7 @@
       <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="30" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3828,7 +3849,7 @@
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="29" t="s">
+      <c r="F31" s="30" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3842,7 +3863,7 @@
       <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="30" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3856,7 +3877,7 @@
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F33" s="30" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3870,7 +3891,7 @@
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F34" s="30" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3884,7 +3905,7 @@
       <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="F35" s="30" t="s">
+      <c r="F35" s="31" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3898,7 +3919,7 @@
       <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="30" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3912,7 +3933,7 @@
       <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="29" t="s">
+      <c r="F37" s="30" t="s">
         <v>124</v>
       </c>
     </row>
@@ -3926,7 +3947,7 @@
       <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="30" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3940,7 +3961,7 @@
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="29" t="s">
+      <c r="F39" s="30" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3954,7 +3975,7 @@
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="29" t="s">
+      <c r="F40" s="30" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3968,7 +3989,7 @@
       <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="30" t="s">
+      <c r="F41" s="31" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3982,7 +4003,7 @@
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="29" t="s">
+      <c r="F42" s="30" t="s">
         <v>134</v>
       </c>
     </row>
@@ -3996,7 +4017,7 @@
       <c r="E43" s="1">
         <v>2</v>
       </c>
-      <c r="F43" s="29" t="s">
+      <c r="F43" s="30" t="s">
         <v>136</v>
       </c>
     </row>
@@ -4010,7 +4031,7 @@
       <c r="E44" s="1">
         <v>2</v>
       </c>
-      <c r="F44" s="29" t="s">
+      <c r="F44" s="30" t="s">
         <v>138</v>
       </c>
     </row>
@@ -4024,7 +4045,7 @@
       <c r="E45" s="1">
         <v>2</v>
       </c>
-      <c r="F45" s="29" t="s">
+      <c r="F45" s="30" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4038,7 +4059,7 @@
       <c r="E46" s="1">
         <v>2</v>
       </c>
-      <c r="F46" s="29" t="s">
+      <c r="F46" s="30" t="s">
         <v>142</v>
       </c>
     </row>
@@ -4052,7 +4073,7 @@
       <c r="E47" s="1">
         <v>2</v>
       </c>
-      <c r="F47" s="30" t="s">
+      <c r="F47" s="31" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4066,7 +4087,7 @@
       <c r="E48" s="1">
         <v>2</v>
       </c>
-      <c r="F48" s="30" t="s">
+      <c r="F48" s="31" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4080,7 +4101,7 @@
       <c r="E49" s="1">
         <v>2</v>
       </c>
-      <c r="F49" s="30" t="s">
+      <c r="F49" s="31" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4094,7 +4115,7 @@
       <c r="E50" s="1">
         <v>2</v>
       </c>
-      <c r="F50" s="30" t="s">
+      <c r="F50" s="31" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4108,7 +4129,7 @@
       <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="30" t="s">
+      <c r="F51" s="31" t="s">
         <v>152</v>
       </c>
     </row>
@@ -4122,7 +4143,7 @@
       <c r="E52" s="1">
         <v>2</v>
       </c>
-      <c r="F52" s="30" t="s">
+      <c r="F52" s="31" t="s">
         <v>154</v>
       </c>
     </row>
@@ -4136,7 +4157,7 @@
       <c r="E53" s="1">
         <v>2</v>
       </c>
-      <c r="F53" s="30" t="s">
+      <c r="F53" s="31" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4150,7 +4171,7 @@
       <c r="E54" s="1">
         <v>2</v>
       </c>
-      <c r="F54" s="30" t="s">
+      <c r="F54" s="31" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4164,7 +4185,7 @@
       <c r="E55" s="1">
         <v>2</v>
       </c>
-      <c r="F55" s="30" t="s">
+      <c r="F55" s="31" t="s">
         <v>160</v>
       </c>
     </row>
@@ -4178,7 +4199,7 @@
       <c r="E56" s="1">
         <v>2</v>
       </c>
-      <c r="F56" s="30" t="s">
+      <c r="F56" s="31" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4192,7 +4213,7 @@
       <c r="E57" s="1">
         <v>2</v>
       </c>
-      <c r="F57" s="30" t="s">
+      <c r="F57" s="31" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4206,7 +4227,7 @@
       <c r="E58" s="1">
         <v>2</v>
       </c>
-      <c r="F58" s="30" t="s">
+      <c r="F58" s="31" t="s">
         <v>166</v>
       </c>
     </row>
@@ -4220,7 +4241,7 @@
       <c r="E59" s="1">
         <v>2</v>
       </c>
-      <c r="F59" s="30" t="s">
+      <c r="F59" s="31" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4234,7 +4255,7 @@
       <c r="E60" s="1">
         <v>2</v>
       </c>
-      <c r="F60" s="30" t="s">
+      <c r="F60" s="31" t="s">
         <v>170</v>
       </c>
     </row>
@@ -4248,7 +4269,7 @@
       <c r="E61" s="1">
         <v>2</v>
       </c>
-      <c r="F61" s="30" t="s">
+      <c r="F61" s="31" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4262,7 +4283,7 @@
       <c r="E62" s="1">
         <v>2</v>
       </c>
-      <c r="F62" s="30" t="s">
+      <c r="F62" s="31" t="s">
         <v>174</v>
       </c>
     </row>
@@ -4276,7 +4297,7 @@
       <c r="E63" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="30" t="s">
+      <c r="F63" s="31" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4290,7 +4311,7 @@
       <c r="E64" s="1">
         <v>2</v>
       </c>
-      <c r="F64" s="30" t="s">
+      <c r="F64" s="31" t="s">
         <v>178</v>
       </c>
     </row>
@@ -4304,7 +4325,7 @@
       <c r="E65" s="1">
         <v>2</v>
       </c>
-      <c r="F65" s="30" t="s">
+      <c r="F65" s="31" t="s">
         <v>180</v>
       </c>
     </row>
@@ -4318,7 +4339,7 @@
       <c r="E66" s="1">
         <v>2</v>
       </c>
-      <c r="F66" s="30" t="s">
+      <c r="F66" s="31" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4332,7 +4353,7 @@
       <c r="E67" s="1">
         <v>2</v>
       </c>
-      <c r="F67" s="30" t="s">
+      <c r="F67" s="31" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4346,7 +4367,7 @@
       <c r="E68" s="1">
         <v>2</v>
       </c>
-      <c r="F68" s="30" t="s">
+      <c r="F68" s="31" t="s">
         <v>186</v>
       </c>
     </row>
@@ -4360,7 +4381,7 @@
       <c r="E69" s="1">
         <v>2</v>
       </c>
-      <c r="F69" s="30" t="s">
+      <c r="F69" s="31" t="s">
         <v>188</v>
       </c>
     </row>
@@ -4374,7 +4395,7 @@
       <c r="E70" s="1">
         <v>2</v>
       </c>
-      <c r="F70" s="30" t="s">
+      <c r="F70" s="31" t="s">
         <v>190</v>
       </c>
     </row>
@@ -4388,7 +4409,7 @@
       <c r="E71" s="1">
         <v>2</v>
       </c>
-      <c r="F71" s="30" t="s">
+      <c r="F71" s="31" t="s">
         <v>192</v>
       </c>
     </row>
@@ -4402,7 +4423,7 @@
       <c r="E72" s="1">
         <v>2</v>
       </c>
-      <c r="F72" s="30" t="s">
+      <c r="F72" s="31" t="s">
         <v>194</v>
       </c>
     </row>
@@ -4416,7 +4437,7 @@
       <c r="E73" s="1">
         <v>2</v>
       </c>
-      <c r="F73" s="30" t="s">
+      <c r="F73" s="31" t="s">
         <v>196</v>
       </c>
     </row>
@@ -4430,7 +4451,7 @@
       <c r="E74" s="1">
         <v>2</v>
       </c>
-      <c r="F74" s="30" t="s">
+      <c r="F74" s="31" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4444,7 +4465,7 @@
       <c r="E75" s="1">
         <v>2</v>
       </c>
-      <c r="F75" s="30" t="s">
+      <c r="F75" s="31" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4458,7 +4479,7 @@
       <c r="E76" s="1">
         <v>2</v>
       </c>
-      <c r="F76" s="30" t="s">
+      <c r="F76" s="31" t="s">
         <v>202</v>
       </c>
     </row>
@@ -4472,7 +4493,7 @@
       <c r="E77" s="1">
         <v>2</v>
       </c>
-      <c r="F77" s="30" t="s">
+      <c r="F77" s="31" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4486,7 +4507,7 @@
       <c r="E78" s="1">
         <v>2</v>
       </c>
-      <c r="F78" s="30" t="s">
+      <c r="F78" s="31" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4500,7 +4521,7 @@
       <c r="E79" s="1">
         <v>2</v>
       </c>
-      <c r="F79" s="30" t="s">
+      <c r="F79" s="31" t="s">
         <v>208</v>
       </c>
     </row>
@@ -4514,7 +4535,7 @@
       <c r="E80" s="1">
         <v>2</v>
       </c>
-      <c r="F80" s="30" t="s">
+      <c r="F80" s="31" t="s">
         <v>210</v>
       </c>
     </row>
@@ -4528,7 +4549,7 @@
       <c r="E81" s="1">
         <v>2</v>
       </c>
-      <c r="F81" s="30" t="s">
+      <c r="F81" s="31" t="s">
         <v>212</v>
       </c>
     </row>
@@ -4542,7 +4563,7 @@
       <c r="E82" s="1">
         <v>2</v>
       </c>
-      <c r="F82" s="30" t="s">
+      <c r="F82" s="31" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4556,12 +4577,12 @@
       <c r="E83" s="1">
         <v>2</v>
       </c>
-      <c r="F83" s="30" t="s">
+      <c r="F83" s="31" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:6">
-      <c r="F89" s="18"/>
+      <c r="F89" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4642,7 +4663,7 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="30" t="s">
         <v>218</v>
       </c>
     </row>
@@ -4656,7 +4677,7 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="30" t="s">
         <v>220</v>
       </c>
     </row>
@@ -4670,7 +4691,7 @@
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="30" t="s">
         <v>222</v>
       </c>
     </row>
@@ -4684,7 +4705,7 @@
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="30" t="s">
         <v>224</v>
       </c>
     </row>
@@ -4698,7 +4719,7 @@
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="30" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4712,7 +4733,7 @@
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="30" t="s">
         <v>228</v>
       </c>
     </row>
@@ -4726,7 +4747,7 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="30" t="s">
         <v>230</v>
       </c>
     </row>
@@ -4740,7 +4761,7 @@
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="30" t="s">
         <v>232</v>
       </c>
     </row>
@@ -4754,7 +4775,7 @@
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="30" t="s">
         <v>234</v>
       </c>
     </row>
@@ -4768,7 +4789,7 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="30" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4782,7 +4803,7 @@
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="30" t="s">
         <v>238</v>
       </c>
     </row>
@@ -4796,7 +4817,7 @@
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="30" t="s">
         <v>240</v>
       </c>
     </row>
@@ -4804,23 +4825,47 @@
       <c r="C18" s="1">
         <v>21013</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>239</v>
+      <c r="D18" s="18" t="s">
+        <v>241</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="29" t="s">
-        <v>240</v>
+      <c r="F18" s="30" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F19" s="16"/>
+      <c r="C19" s="1">
+        <v>21014</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F20" s="16"/>
+      <c r="C20" s="1">
+        <v>21015</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="D21" s="18"/>
+      <c r="E21" s="1"/>
       <c r="F21" s="16"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4962,13 +5007,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
-      <c r="F6" s="31" t="s">
-        <v>242</v>
+      <c r="F6" s="32" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -4976,13 +5021,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
-      <c r="F7" s="31" t="s">
-        <v>244</v>
+      <c r="F7" s="32" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -4990,13 +5035,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>246</v>
+      <c r="F8" s="32" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -5004,13 +5049,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
-      <c r="F9" s="31" t="s">
-        <v>248</v>
+      <c r="F9" s="32" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -5018,13 +5063,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
-      <c r="F10" s="31" t="s">
-        <v>250</v>
+      <c r="F10" s="32" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -5032,13 +5077,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
-      <c r="F11" s="31" t="s">
-        <v>252</v>
+      <c r="F11" s="32" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -5046,13 +5091,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>254</v>
+      <c r="F12" s="32" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -5060,13 +5105,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
-      <c r="F13" s="31" t="s">
-        <v>256</v>
+      <c r="F13" s="32" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -5074,13 +5119,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
-      <c r="F14" s="31" t="s">
-        <v>258</v>
+      <c r="F14" s="32" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -5088,13 +5133,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
-      <c r="F15" s="31" t="s">
-        <v>260</v>
+      <c r="F15" s="32" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -5102,13 +5147,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
-      <c r="F16" s="31" t="s">
-        <v>262</v>
+      <c r="F16" s="32" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -5116,13 +5161,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
-      <c r="F17" s="31" t="s">
-        <v>264</v>
+      <c r="F17" s="32" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -5130,13 +5175,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
-      <c r="F18" s="31" t="s">
-        <v>266</v>
+      <c r="F18" s="32" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -5144,13 +5189,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
-      <c r="F19" s="31" t="s">
-        <v>268</v>
+      <c r="F19" s="32" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -5158,13 +5203,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
-      <c r="F20" s="31" t="s">
-        <v>270</v>
+      <c r="F20" s="32" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -5172,13 +5217,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
-      <c r="F21" s="31" t="s">
-        <v>272</v>
+      <c r="F21" s="32" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -5186,13 +5231,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
-      <c r="F22" s="31" t="s">
-        <v>274</v>
+      <c r="F22" s="32" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -5200,13 +5245,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
-      <c r="F23" s="31" t="s">
-        <v>276</v>
+      <c r="F23" s="32" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -5214,13 +5259,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
-      <c r="F24" s="31" t="s">
-        <v>278</v>
+      <c r="F24" s="32" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -5228,13 +5273,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
-      <c r="F25" s="31" t="s">
-        <v>280</v>
+      <c r="F25" s="32" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -5242,13 +5287,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
-      <c r="F26" s="31" t="s">
-        <v>282</v>
+      <c r="F26" s="32" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -5256,13 +5301,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
-      <c r="F27" s="31" t="s">
-        <v>284</v>
+      <c r="F27" s="32" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -5270,13 +5315,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
-      <c r="F28" s="31" t="s">
-        <v>286</v>
+      <c r="F28" s="32" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -5284,13 +5329,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
-      <c r="F29" s="31" t="s">
-        <v>288</v>
+      <c r="F29" s="32" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -5298,13 +5343,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>290</v>
+      <c r="F30" s="32" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -5312,13 +5357,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
-      <c r="F31" s="31" t="s">
-        <v>292</v>
+      <c r="F31" s="32" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -5326,13 +5371,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
-      <c r="F32" s="31" t="s">
-        <v>294</v>
+      <c r="F32" s="32" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -5340,13 +5385,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
-      <c r="F33" s="31" t="s">
-        <v>296</v>
+      <c r="F33" s="32" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -5354,13 +5399,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
-      <c r="F34" s="31" t="s">
-        <v>298</v>
+      <c r="F34" s="32" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -5368,13 +5413,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
-      <c r="F35" s="31" t="s">
-        <v>300</v>
+      <c r="F35" s="32" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -5382,13 +5427,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
-      <c r="F36" s="31" t="s">
-        <v>302</v>
+      <c r="F36" s="32" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -5396,13 +5441,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
-      <c r="F37" s="31" t="s">
-        <v>304</v>
+      <c r="F37" s="32" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -5410,13 +5455,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
-      <c r="F38" s="31" t="s">
-        <v>306</v>
+      <c r="F38" s="32" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -5424,13 +5469,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
-      <c r="F39" s="31" t="s">
-        <v>308</v>
+      <c r="F39" s="32" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -5438,13 +5483,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
-      <c r="F40" s="31" t="s">
-        <v>310</v>
+      <c r="F40" s="32" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -5452,13 +5497,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
-      <c r="F41" s="31" t="s">
-        <v>312</v>
+      <c r="F41" s="32" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -5466,13 +5511,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
-      <c r="F42" s="31" t="s">
-        <v>314</v>
+      <c r="F42" s="32" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -5480,13 +5525,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
-      <c r="F43" s="31" t="s">
-        <v>316</v>
+      <c r="F43" s="32" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -5494,13 +5539,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
-      <c r="F44" s="31" t="s">
-        <v>318</v>
+      <c r="F44" s="32" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -5508,13 +5553,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
-      <c r="F45" s="31" t="s">
-        <v>320</v>
+      <c r="F45" s="32" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -5522,13 +5567,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
-      <c r="F46" s="31" t="s">
-        <v>322</v>
+      <c r="F46" s="32" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -5536,13 +5581,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
-      <c r="F47" s="31" t="s">
-        <v>324</v>
+      <c r="F47" s="32" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -5550,13 +5595,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
-      <c r="F48" s="31" t="s">
-        <v>326</v>
+      <c r="F48" s="32" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -5564,13 +5609,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
-      <c r="F49" s="31" t="s">
-        <v>328</v>
+      <c r="F49" s="32" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -5578,13 +5623,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
-      <c r="F50" s="31" t="s">
-        <v>330</v>
+      <c r="F50" s="32" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -5592,13 +5637,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
-      <c r="F51" s="31" t="s">
-        <v>332</v>
+      <c r="F51" s="32" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -5606,13 +5651,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
-      <c r="F52" s="31" t="s">
-        <v>334</v>
+      <c r="F52" s="32" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -5620,13 +5665,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
-      <c r="F53" s="31" t="s">
-        <v>335</v>
+      <c r="F53" s="32" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -5634,13 +5679,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
-      <c r="F54" s="31" t="s">
-        <v>337</v>
+      <c r="F54" s="32" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -5648,13 +5693,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
-      <c r="F55" s="31" t="s">
-        <v>339</v>
+      <c r="F55" s="32" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -5662,13 +5707,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
-      <c r="F56" s="31" t="s">
-        <v>341</v>
+      <c r="F56" s="32" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -5676,13 +5721,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
-      <c r="F57" s="31" t="s">
-        <v>343</v>
+      <c r="F57" s="32" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -5690,13 +5735,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
-      <c r="F58" s="31" t="s">
-        <v>345</v>
+      <c r="F58" s="32" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -5704,13 +5749,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
-      <c r="F59" s="31" t="s">
-        <v>347</v>
+      <c r="F59" s="32" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -5718,13 +5763,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
-      <c r="F60" s="31" t="s">
-        <v>349</v>
+      <c r="F60" s="32" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -5732,13 +5777,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
-      <c r="F61" s="31" t="s">
-        <v>351</v>
+      <c r="F61" s="32" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -5746,13 +5791,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
-      <c r="F62" s="31" t="s">
-        <v>352</v>
+      <c r="F62" s="32" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -5760,13 +5805,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
-      <c r="F63" s="31" t="s">
-        <v>354</v>
+      <c r="F63" s="32" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -5774,13 +5819,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
-      <c r="F64" s="31" t="s">
-        <v>356</v>
+      <c r="F64" s="32" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -5788,13 +5833,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
-      <c r="F65" s="31" t="s">
-        <v>358</v>
+      <c r="F65" s="32" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -5802,13 +5847,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
-      <c r="F66" s="31" t="s">
-        <v>360</v>
+      <c r="F66" s="32" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -5816,13 +5861,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
-      <c r="F67" s="31" t="s">
-        <v>362</v>
+      <c r="F67" s="32" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -5830,13 +5875,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
-      <c r="F68" s="31" t="s">
-        <v>364</v>
+      <c r="F68" s="32" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -5844,13 +5889,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
-      <c r="F69" s="31" t="s">
-        <v>366</v>
+      <c r="F69" s="32" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -5858,13 +5903,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
-      <c r="F70" s="31" t="s">
-        <v>368</v>
+      <c r="F70" s="32" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -5872,13 +5917,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
-      <c r="F71" s="31" t="s">
-        <v>370</v>
+      <c r="F71" s="32" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -5886,13 +5931,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
-      <c r="F72" s="31" t="s">
-        <v>371</v>
+      <c r="F72" s="32" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -5900,13 +5945,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
-      <c r="F73" s="31" t="s">
-        <v>373</v>
+      <c r="F73" s="32" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -5914,13 +5959,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
-      <c r="F74" s="31" t="s">
-        <v>375</v>
+      <c r="F74" s="32" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5928,13 +5973,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
-      <c r="F75" s="31" t="s">
-        <v>377</v>
+      <c r="F75" s="32" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -5942,13 +5987,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
-      <c r="F76" s="31" t="s">
-        <v>379</v>
+      <c r="F76" s="32" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -5956,13 +6001,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
-      <c r="F77" s="31" t="s">
-        <v>381</v>
+      <c r="F77" s="32" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:6">
@@ -5970,13 +6015,13 @@
         <v>180073</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="E78" s="6">
         <v>18</v>
       </c>
-      <c r="F78" s="31" t="s">
-        <v>383</v>
+      <c r="F78" s="32" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -6058,13 +6103,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -6150,13 +6195,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="32" t="s">
-        <v>387</v>
+      <c r="F6" s="33" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6164,13 +6209,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="32" t="s">
-        <v>389</v>
+      <c r="F7" s="33" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6178,13 +6223,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F8" s="32" t="s">
-        <v>391</v>
+      <c r="F8" s="33" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6192,13 +6237,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="32" t="s">
-        <v>393</v>
+      <c r="F9" s="33" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6206,13 +6251,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
-      <c r="F10" s="32" t="s">
-        <v>395</v>
+      <c r="F10" s="33" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6220,13 +6265,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="32" t="s">
-        <v>397</v>
+      <c r="F11" s="33" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6234,13 +6279,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>399</v>
+      <c r="F12" s="33" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6248,13 +6293,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
-      <c r="F13" s="33" t="s">
-        <v>401</v>
+      <c r="F13" s="34" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -6262,13 +6307,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
-      <c r="F14" s="33" t="s">
-        <v>403</v>
+      <c r="F14" s="34" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -6378,13 +6423,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
-      <c r="F6" s="31" t="s">
-        <v>405</v>
+      <c r="F6" s="32" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6392,13 +6437,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
-      <c r="F7" s="31" t="s">
-        <v>407</v>
+      <c r="F7" s="32" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6406,13 +6451,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>409</v>
+      <c r="F8" s="32" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6420,13 +6465,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
-      <c r="F9" s="31" t="s">
-        <v>411</v>
+      <c r="F9" s="32" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6434,13 +6479,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
-      <c r="F10" s="31" t="s">
-        <v>413</v>
+      <c r="F10" s="32" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6448,13 +6493,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="31" t="s">
-        <v>415</v>
+      <c r="F11" s="32" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6462,13 +6507,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>417</v>
+      <c r="F12" s="32" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6476,13 +6521,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
-      <c r="F13" s="31" t="s">
-        <v>419</v>
+      <c r="F13" s="32" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6490,13 +6535,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
-      <c r="F14" s="31" t="s">
-        <v>421</v>
+      <c r="F14" s="32" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -6504,13 +6549,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
-      <c r="F15" s="31" t="s">
-        <v>423</v>
+      <c r="F15" s="32" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -6518,13 +6563,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
-      <c r="F16" s="31" t="s">
-        <v>425</v>
+      <c r="F16" s="32" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -6532,13 +6577,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
-      <c r="F17" s="31" t="s">
-        <v>427</v>
+      <c r="F17" s="32" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -6546,13 +6591,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
-      <c r="F18" s="31" t="s">
-        <v>429</v>
+      <c r="F18" s="32" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -6560,13 +6605,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
-      <c r="F19" s="31" t="s">
-        <v>431</v>
+      <c r="F19" s="32" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -6574,13 +6619,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
-      <c r="F20" s="31" t="s">
-        <v>433</v>
+      <c r="F20" s="32" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -6588,13 +6633,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
-      <c r="F21" s="31" t="s">
-        <v>435</v>
+      <c r="F21" s="32" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -6602,13 +6647,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
-      <c r="F22" s="31" t="s">
-        <v>437</v>
+      <c r="F22" s="32" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -6616,13 +6661,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
-      <c r="F23" s="31" t="s">
-        <v>439</v>
+      <c r="F23" s="32" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6630,13 +6675,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
-      <c r="F24" s="31" t="s">
-        <v>441</v>
+      <c r="F24" s="32" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6644,13 +6689,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
-      <c r="F25" s="31" t="s">
-        <v>443</v>
+      <c r="F25" s="32" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6658,13 +6703,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
-      <c r="F26" s="31" t="s">
-        <v>445</v>
+      <c r="F26" s="32" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6672,13 +6717,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
-      <c r="F27" s="31" t="s">
-        <v>447</v>
+      <c r="F27" s="32" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6686,13 +6731,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
-      <c r="F28" s="31" t="s">
-        <v>449</v>
+      <c r="F28" s="32" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6700,13 +6745,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
-      <c r="F29" s="31" t="s">
-        <v>451</v>
+      <c r="F29" s="32" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6714,13 +6759,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>453</v>
+      <c r="F30" s="32" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6728,13 +6773,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
-      <c r="F31" s="31" t="s">
-        <v>455</v>
+      <c r="F31" s="32" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6742,13 +6787,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
-      <c r="F32" s="31" t="s">
-        <v>457</v>
+      <c r="F32" s="32" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -6756,13 +6801,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
-      <c r="F33" s="31" t="s">
-        <v>459</v>
+      <c r="F33" s="32" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -6770,13 +6815,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
-      <c r="F34" s="31" t="s">
-        <v>461</v>
+      <c r="F34" s="32" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -6784,13 +6829,13 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
-      <c r="F35" s="31" t="s">
-        <v>463</v>
+      <c r="F35" s="32" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -6798,13 +6843,13 @@
         <v>50031</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
       </c>
-      <c r="F36" s="31" t="s">
-        <v>465</v>
+      <c r="F36" s="32" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -6812,13 +6857,13 @@
         <v>50032</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
       </c>
-      <c r="F37" s="31" t="s">
-        <v>467</v>
+      <c r="F37" s="32" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -6826,13 +6871,13 @@
         <v>50033</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
       </c>
-      <c r="F38" s="31" t="s">
-        <v>469</v>
+      <c r="F38" s="32" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -6840,13 +6885,13 @@
         <v>50034</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
       </c>
-      <c r="F39" s="31" t="s">
-        <v>471</v>
+      <c r="F39" s="32" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -6854,13 +6899,13 @@
         <v>50035</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
       </c>
-      <c r="F40" s="31" t="s">
-        <v>473</v>
+      <c r="F40" s="32" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -6868,13 +6913,13 @@
         <v>50036</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
       </c>
-      <c r="F41" s="31" t="s">
-        <v>475</v>
+      <c r="F41" s="32" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -6882,13 +6927,13 @@
         <v>50037</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E42" s="1">
         <v>6</v>
       </c>
-      <c r="F42" s="30" t="s">
-        <v>477</v>
+      <c r="F42" s="31" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -6896,13 +6941,13 @@
         <v>50038</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E43" s="1">
         <v>6</v>
       </c>
-      <c r="F43" s="30" t="s">
-        <v>478</v>
+      <c r="F43" s="31" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -6910,13 +6955,13 @@
         <v>50039</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E44" s="1">
         <v>6</v>
       </c>
-      <c r="F44" s="30" t="s">
-        <v>479</v>
+      <c r="F44" s="31" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -6924,13 +6969,13 @@
         <v>50040</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E45" s="1">
         <v>6</v>
       </c>
-      <c r="F45" s="30" t="s">
-        <v>480</v>
+      <c r="F45" s="31" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -6938,13 +6983,13 @@
         <v>50041</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E46" s="1">
         <v>6</v>
       </c>
-      <c r="F46" s="30" t="s">
-        <v>481</v>
+      <c r="F46" s="31" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -6952,13 +6997,13 @@
         <v>50042</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E47" s="1">
         <v>6</v>
       </c>
-      <c r="F47" s="30" t="s">
-        <v>482</v>
+      <c r="F47" s="31" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="491">
   <si>
     <t>_id</t>
   </si>
@@ -555,6 +555,12 @@
   </si>
   <si>
     <t>5007</t>
+  </si>
+  <si>
+    <t>凤凰之羽</t>
+  </si>
+  <si>
+    <t>5008</t>
   </si>
   <si>
     <t>魂环1</t>
@@ -2143,12 +2149,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2608,7 +2614,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2647,9 +2653,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3012,413 +3015,424 @@
   <dimension ref="C1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="9" style="20"/>
-    <col min="3" max="3" width="8.75" style="20" customWidth="1"/>
-    <col min="4" max="4" width="17.8333333333333" style="20" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="20" customWidth="1"/>
-    <col min="6" max="6" width="30.75" style="21" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="20"/>
+    <col min="1" max="2" width="9" style="19"/>
+    <col min="3" max="3" width="8.75" style="19" customWidth="1"/>
+    <col min="4" max="4" width="17.8333333333333" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="19" customWidth="1"/>
+    <col min="6" max="6" width="30.75" style="20" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" s="20" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F1" s="21"/>
-    </row>
-    <row r="2" s="20" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" s="20" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C3" s="22" t="s">
+    <row r="1" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F1" s="20"/>
+    </row>
+    <row r="2" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F2" s="20"/>
+    </row>
+    <row r="3" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="20" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C4" s="22" t="s">
+    <row r="4" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="20" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C5" s="22" t="s">
+    <row r="5" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="22" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="20" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="20">
+    <row r="6" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="19">
         <v>1</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <v>5</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="26" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
-      <c r="C7" s="20">
-        <v>2</v>
-      </c>
-      <c r="D7" s="20" t="s">
+      <c r="C7" s="19">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <v>5</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="26" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
-      <c r="C8" s="20">
+      <c r="C8" s="19">
         <v>3</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <v>5</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="26" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>4</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="19">
         <v>5</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="26" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>5</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="19">
         <v>6</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="27" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <v>6</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="19">
         <v>6</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
-      <c r="C12" s="20">
+      <c r="C12" s="19">
         <v>7</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="19">
         <v>6</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="27" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
-      <c r="C13" s="20">
+      <c r="C13" s="19">
         <v>8</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="19">
         <v>6</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="27" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
-      <c r="C14" s="20">
+      <c r="C14" s="19">
         <v>9</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="19">
         <v>6</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="27" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
-      <c r="C15" s="20">
+      <c r="C15" s="19">
         <v>10</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="19">
         <v>6</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="27" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
-      <c r="C16" s="20">
+      <c r="C16" s="19">
         <v>11</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="19">
         <v>5</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="20" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="20">
+      <c r="C17" s="19">
         <v>12</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="19">
         <v>5</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="20" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="20">
+      <c r="C18" s="19">
         <v>13</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="19">
         <v>5</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="20">
+      <c r="C19" s="19">
         <v>14</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="19">
         <v>5</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="20" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="20">
+      <c r="C20" s="19">
         <v>15</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="19">
         <v>5</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="20" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
-      <c r="C21" s="20">
+      <c r="C21" s="19">
         <v>16</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="19">
         <v>5</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="20" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" s="20" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C22" s="25"/>
+    <row r="22" s="19" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C22" s="24">
+        <v>17</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="19">
+        <v>5</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
-      <c r="C26" s="20">
+      <c r="C26" s="19">
         <v>21</v>
       </c>
-      <c r="D26" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="20">
+      <c r="D26" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="19">
         <v>5</v>
       </c>
-      <c r="F26" s="29" t="s">
-        <v>44</v>
+      <c r="F26" s="28" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
-      <c r="C27" s="20">
+      <c r="C27" s="19">
         <v>22</v>
       </c>
-      <c r="D27" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="20">
+      <c r="D27" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="19">
         <v>5</v>
       </c>
-      <c r="F27" s="29" t="s">
-        <v>46</v>
+      <c r="F27" s="28" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
-      <c r="C28" s="20">
+      <c r="C28" s="19">
         <v>23</v>
       </c>
-      <c r="D28" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="20">
+      <c r="D28" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="19">
         <v>5</v>
       </c>
-      <c r="F28" s="29" t="s">
-        <v>48</v>
+      <c r="F28" s="28" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
-      <c r="C29" s="20">
+      <c r="C29" s="19">
         <v>24</v>
       </c>
-      <c r="D29" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="20">
+      <c r="D29" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="19">
         <v>5</v>
       </c>
-      <c r="F29" s="29" t="s">
-        <v>50</v>
+      <c r="F29" s="28" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
-      <c r="C30" s="20">
+      <c r="C30" s="19">
         <v>25</v>
       </c>
-      <c r="D30" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="20">
+      <c r="D30" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="19">
         <v>5</v>
       </c>
-      <c r="F30" s="29" t="s">
-        <v>52</v>
+      <c r="F30" s="28" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
-      <c r="C31" s="20">
+      <c r="C31" s="19">
         <v>26</v>
       </c>
-      <c r="D31" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="20">
+      <c r="D31" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="19">
         <v>5</v>
       </c>
-      <c r="F31" s="29" t="s">
-        <v>54</v>
+      <c r="F31" s="28" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
-      <c r="C32" s="20">
+      <c r="C32" s="19">
         <v>27</v>
       </c>
-      <c r="D32" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="20">
+      <c r="D32" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="19">
         <v>5</v>
       </c>
-      <c r="F32" s="29" t="s">
-        <v>56</v>
+      <c r="F32" s="28" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
-      <c r="C33" s="20">
+      <c r="C33" s="19">
         <v>28</v>
       </c>
-      <c r="D33" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="20">
+      <c r="D33" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="19">
         <v>5</v>
       </c>
-      <c r="F33" s="29" t="s">
-        <v>58</v>
+      <c r="F33" s="28" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
-      <c r="C34" s="20">
+      <c r="C34" s="19">
         <v>29</v>
       </c>
-      <c r="D34" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E34" s="20">
+      <c r="D34" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="19">
         <v>5</v>
       </c>
-      <c r="F34" s="28" t="s">
-        <v>60</v>
+      <c r="F34" s="27" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3494,13 +3508,13 @@
         <v>20001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="30" t="s">
-        <v>62</v>
+      <c r="F6" s="29" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -3508,13 +3522,13 @@
         <v>20002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="30" t="s">
-        <v>64</v>
+      <c r="F7" s="29" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -3522,13 +3536,13 @@
         <v>20003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="30" t="s">
-        <v>66</v>
+      <c r="F8" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -3536,13 +3550,13 @@
         <v>20004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="30" t="s">
-        <v>68</v>
+      <c r="F9" s="29" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -3550,13 +3564,13 @@
         <v>20005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="30" t="s">
-        <v>70</v>
+      <c r="F10" s="29" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -3564,13 +3578,13 @@
         <v>20006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="31" t="s">
-        <v>72</v>
+      <c r="F11" s="30" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -3578,13 +3592,13 @@
         <v>20007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>74</v>
+      <c r="F12" s="29" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -3592,13 +3606,13 @@
         <v>20008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="30" t="s">
-        <v>76</v>
+      <c r="F13" s="29" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -3606,13 +3620,13 @@
         <v>20009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="30" t="s">
-        <v>78</v>
+      <c r="F14" s="29" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -3620,13 +3634,13 @@
         <v>20010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="30" t="s">
-        <v>80</v>
+      <c r="F15" s="29" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -3634,13 +3648,13 @@
         <v>20011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="30" t="s">
-        <v>82</v>
+      <c r="F16" s="29" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -3648,13 +3662,13 @@
         <v>20012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="31" t="s">
-        <v>84</v>
+      <c r="F17" s="30" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -3662,13 +3676,13 @@
         <v>20013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="30" t="s">
-        <v>86</v>
+      <c r="F18" s="29" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -3676,13 +3690,13 @@
         <v>20014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="30" t="s">
-        <v>88</v>
+      <c r="F19" s="29" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -3690,13 +3704,13 @@
         <v>20015</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="30" t="s">
-        <v>90</v>
+      <c r="F20" s="29" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -3704,13 +3718,13 @@
         <v>20016</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="30" t="s">
-        <v>92</v>
+      <c r="F21" s="29" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -3718,13 +3732,13 @@
         <v>20017</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="30" t="s">
-        <v>94</v>
+      <c r="F22" s="29" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -3732,13 +3746,13 @@
         <v>20018</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="31" t="s">
-        <v>96</v>
+      <c r="F23" s="30" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -3746,13 +3760,13 @@
         <v>20019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="30" t="s">
-        <v>98</v>
+      <c r="F24" s="29" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -3760,13 +3774,13 @@
         <v>20020</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="30" t="s">
-        <v>100</v>
+      <c r="F25" s="29" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -3774,13 +3788,13 @@
         <v>20021</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="30" t="s">
-        <v>102</v>
+      <c r="F26" s="29" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -3788,13 +3802,13 @@
         <v>20022</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="30" t="s">
-        <v>104</v>
+      <c r="F27" s="29" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -3802,13 +3816,13 @@
         <v>20023</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="30" t="s">
-        <v>106</v>
+      <c r="F28" s="29" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -3816,13 +3830,13 @@
         <v>20024</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="31" t="s">
-        <v>108</v>
+      <c r="F29" s="30" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -3830,13 +3844,13 @@
         <v>20025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="30" t="s">
-        <v>110</v>
+      <c r="F30" s="29" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -3844,13 +3858,13 @@
         <v>20026</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="30" t="s">
-        <v>112</v>
+      <c r="F31" s="29" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -3858,13 +3872,13 @@
         <v>20027</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="30" t="s">
-        <v>114</v>
+      <c r="F32" s="29" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -3872,13 +3886,13 @@
         <v>20028</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="30" t="s">
-        <v>116</v>
+      <c r="F33" s="29" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -3886,13 +3900,13 @@
         <v>20029</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="30" t="s">
-        <v>118</v>
+      <c r="F34" s="29" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -3900,13 +3914,13 @@
         <v>20030</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="F35" s="31" t="s">
-        <v>120</v>
+      <c r="F35" s="30" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -3914,13 +3928,13 @@
         <v>20031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="30" t="s">
-        <v>122</v>
+      <c r="F36" s="29" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -3928,13 +3942,13 @@
         <v>20032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="30" t="s">
-        <v>124</v>
+      <c r="F37" s="29" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -3942,13 +3956,13 @@
         <v>20033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="30" t="s">
-        <v>126</v>
+      <c r="F38" s="29" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -3956,13 +3970,13 @@
         <v>20034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="30" t="s">
-        <v>128</v>
+      <c r="F39" s="29" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -3970,13 +3984,13 @@
         <v>20035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="30" t="s">
-        <v>130</v>
+      <c r="F40" s="29" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -3984,13 +3998,13 @@
         <v>20036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="31" t="s">
-        <v>132</v>
+      <c r="F41" s="30" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -3998,13 +4012,13 @@
         <v>20037</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="30" t="s">
-        <v>134</v>
+      <c r="F42" s="29" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -4012,13 +4026,13 @@
         <v>20038</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
-      <c r="F43" s="30" t="s">
-        <v>136</v>
+      <c r="F43" s="29" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -4026,13 +4040,13 @@
         <v>20039</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
-      <c r="F44" s="30" t="s">
-        <v>138</v>
+      <c r="F44" s="29" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -4040,13 +4054,13 @@
         <v>20040</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
-      <c r="F45" s="30" t="s">
-        <v>140</v>
+      <c r="F45" s="29" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -4054,13 +4068,13 @@
         <v>20041</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
-      <c r="F46" s="30" t="s">
-        <v>142</v>
+      <c r="F46" s="29" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -4068,13 +4082,13 @@
         <v>20042</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
-      <c r="F47" s="31" t="s">
-        <v>144</v>
+      <c r="F47" s="30" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -4082,13 +4096,13 @@
         <v>20043</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
-      <c r="F48" s="31" t="s">
-        <v>146</v>
+      <c r="F48" s="30" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -4096,13 +4110,13 @@
         <v>20044</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
-      <c r="F49" s="31" t="s">
-        <v>148</v>
+      <c r="F49" s="30" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -4110,13 +4124,13 @@
         <v>20045</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
-      <c r="F50" s="31" t="s">
-        <v>150</v>
+      <c r="F50" s="30" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -4124,13 +4138,13 @@
         <v>20046</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="31" t="s">
-        <v>152</v>
+      <c r="F51" s="30" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -4138,13 +4152,13 @@
         <v>20047</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
-      <c r="F52" s="31" t="s">
-        <v>154</v>
+      <c r="F52" s="30" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -4152,13 +4166,13 @@
         <v>20048</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
-      <c r="F53" s="31" t="s">
-        <v>156</v>
+      <c r="F53" s="30" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -4166,13 +4180,13 @@
         <v>20049</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
-      <c r="F54" s="31" t="s">
-        <v>158</v>
+      <c r="F54" s="30" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -4180,13 +4194,13 @@
         <v>20050</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
-      <c r="F55" s="31" t="s">
-        <v>160</v>
+      <c r="F55" s="30" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -4194,13 +4208,13 @@
         <v>20051</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
-      <c r="F56" s="31" t="s">
-        <v>162</v>
+      <c r="F56" s="30" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -4208,13 +4222,13 @@
         <v>20052</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
-      <c r="F57" s="31" t="s">
-        <v>164</v>
+      <c r="F57" s="30" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -4222,13 +4236,13 @@
         <v>20053</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
-      <c r="F58" s="31" t="s">
-        <v>166</v>
+      <c r="F58" s="30" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -4236,13 +4250,13 @@
         <v>20054</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
-      <c r="F59" s="31" t="s">
-        <v>168</v>
+      <c r="F59" s="30" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -4250,13 +4264,13 @@
         <v>20055</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
-      <c r="F60" s="31" t="s">
-        <v>170</v>
+      <c r="F60" s="30" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -4264,13 +4278,13 @@
         <v>20056</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
-      <c r="F61" s="31" t="s">
-        <v>172</v>
+      <c r="F61" s="30" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -4278,13 +4292,13 @@
         <v>20057</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
-      <c r="F62" s="31" t="s">
-        <v>174</v>
+      <c r="F62" s="30" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -4292,13 +4306,13 @@
         <v>20058</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="31" t="s">
-        <v>176</v>
+      <c r="F63" s="30" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -4306,13 +4320,13 @@
         <v>20059</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
-      <c r="F64" s="31" t="s">
-        <v>178</v>
+      <c r="F64" s="30" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -4320,13 +4334,13 @@
         <v>20060</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
-      <c r="F65" s="31" t="s">
-        <v>180</v>
+      <c r="F65" s="30" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -4334,13 +4348,13 @@
         <v>20061</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
-      <c r="F66" s="31" t="s">
-        <v>182</v>
+      <c r="F66" s="30" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -4348,13 +4362,13 @@
         <v>20062</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
-      <c r="F67" s="31" t="s">
-        <v>184</v>
+      <c r="F67" s="30" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -4362,13 +4376,13 @@
         <v>20063</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
-      <c r="F68" s="31" t="s">
-        <v>186</v>
+      <c r="F68" s="30" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -4376,13 +4390,13 @@
         <v>20064</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
-      <c r="F69" s="31" t="s">
-        <v>188</v>
+      <c r="F69" s="30" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -4390,13 +4404,13 @@
         <v>20065</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
-      <c r="F70" s="31" t="s">
-        <v>190</v>
+      <c r="F70" s="30" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -4404,13 +4418,13 @@
         <v>20066</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
-      <c r="F71" s="31" t="s">
-        <v>192</v>
+      <c r="F71" s="30" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -4418,13 +4432,13 @@
         <v>20067</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
-      <c r="F72" s="31" t="s">
-        <v>194</v>
+      <c r="F72" s="30" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -4432,13 +4446,13 @@
         <v>20068</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
-      <c r="F73" s="31" t="s">
-        <v>196</v>
+      <c r="F73" s="30" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -4446,13 +4460,13 @@
         <v>20069</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
-      <c r="F74" s="31" t="s">
-        <v>198</v>
+      <c r="F74" s="30" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -4460,13 +4474,13 @@
         <v>20070</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
-      <c r="F75" s="31" t="s">
-        <v>200</v>
+      <c r="F75" s="30" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -4474,13 +4488,13 @@
         <v>20071</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
       </c>
-      <c r="F76" s="31" t="s">
-        <v>202</v>
+      <c r="F76" s="30" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -4488,13 +4502,13 @@
         <v>20072</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
       </c>
-      <c r="F77" s="31" t="s">
-        <v>204</v>
+      <c r="F77" s="30" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:6">
@@ -4502,13 +4516,13 @@
         <v>20073</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
       </c>
-      <c r="F78" s="31" t="s">
-        <v>206</v>
+      <c r="F78" s="30" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:6">
@@ -4516,13 +4530,13 @@
         <v>20074</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
       </c>
-      <c r="F79" s="31" t="s">
-        <v>208</v>
+      <c r="F79" s="30" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:6">
@@ -4530,13 +4544,13 @@
         <v>20075</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
       </c>
-      <c r="F80" s="31" t="s">
-        <v>210</v>
+      <c r="F80" s="30" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:6">
@@ -4544,13 +4558,13 @@
         <v>20076</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
       </c>
-      <c r="F81" s="31" t="s">
-        <v>212</v>
+      <c r="F81" s="30" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:6">
@@ -4558,13 +4572,13 @@
         <v>20077</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
       </c>
-      <c r="F82" s="31" t="s">
-        <v>214</v>
+      <c r="F82" s="30" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:6">
@@ -4572,17 +4586,17 @@
         <v>20078</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
       </c>
-      <c r="F83" s="31" t="s">
-        <v>216</v>
+      <c r="F83" s="30" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:6">
-      <c r="F89" s="19"/>
+      <c r="F89" s="18"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4658,13 +4672,13 @@
         <v>21001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="30" t="s">
-        <v>218</v>
+      <c r="F6" s="29" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4672,13 +4686,13 @@
         <v>21002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="30" t="s">
-        <v>220</v>
+      <c r="F7" s="29" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4686,13 +4700,13 @@
         <v>21003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="30" t="s">
-        <v>222</v>
+      <c r="F8" s="29" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4700,13 +4714,13 @@
         <v>21004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="30" t="s">
-        <v>224</v>
+      <c r="F9" s="29" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4714,13 +4728,13 @@
         <v>21005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="30" t="s">
-        <v>226</v>
+      <c r="F10" s="29" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4728,13 +4742,13 @@
         <v>21006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="30" t="s">
-        <v>228</v>
+      <c r="F11" s="29" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4742,13 +4756,13 @@
         <v>21007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>230</v>
+      <c r="F12" s="29" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4756,13 +4770,13 @@
         <v>21008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="30" t="s">
-        <v>232</v>
+      <c r="F13" s="29" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4770,13 +4784,13 @@
         <v>21009</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="30" t="s">
-        <v>234</v>
+      <c r="F14" s="29" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4784,13 +4798,13 @@
         <v>21010</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="30" t="s">
-        <v>236</v>
+      <c r="F15" s="29" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4798,13 +4812,13 @@
         <v>21011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="30" t="s">
-        <v>238</v>
+      <c r="F16" s="29" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4812,59 +4826,59 @@
         <v>21012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="30" t="s">
-        <v>240</v>
+      <c r="F17" s="29" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C18" s="1">
         <v>21013</v>
       </c>
-      <c r="D18" s="18" t="s">
-        <v>241</v>
+      <c r="D18" s="17" t="s">
+        <v>243</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="30" t="s">
-        <v>242</v>
+      <c r="F18" s="29" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C19" s="1">
         <v>21014</v>
       </c>
-      <c r="D19" s="18" t="s">
-        <v>243</v>
+      <c r="D19" s="17" t="s">
+        <v>245</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="30" t="s">
-        <v>244</v>
+      <c r="F19" s="29" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C20" s="1">
         <v>21015</v>
       </c>
-      <c r="D20" s="18" t="s">
-        <v>245</v>
+      <c r="D20" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="30" t="s">
-        <v>246</v>
+      <c r="F20" s="29" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="D21" s="18"/>
+      <c r="D21" s="17"/>
       <c r="E21" s="1"/>
       <c r="F21" s="16"/>
     </row>
@@ -5007,13 +5021,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
-      <c r="F6" s="32" t="s">
-        <v>248</v>
+      <c r="F6" s="31" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -5021,13 +5035,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
-      <c r="F7" s="32" t="s">
-        <v>250</v>
+      <c r="F7" s="31" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -5035,13 +5049,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
-      <c r="F8" s="32" t="s">
-        <v>252</v>
+      <c r="F8" s="31" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -5049,13 +5063,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
-      <c r="F9" s="32" t="s">
-        <v>254</v>
+      <c r="F9" s="31" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -5063,13 +5077,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
-      <c r="F10" s="32" t="s">
-        <v>256</v>
+      <c r="F10" s="31" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -5077,13 +5091,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
-      <c r="F11" s="32" t="s">
-        <v>258</v>
+      <c r="F11" s="31" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -5091,13 +5105,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>260</v>
+      <c r="F12" s="31" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -5105,13 +5119,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
-      <c r="F13" s="32" t="s">
-        <v>262</v>
+      <c r="F13" s="31" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -5119,13 +5133,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
-      <c r="F14" s="32" t="s">
-        <v>264</v>
+      <c r="F14" s="31" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -5133,13 +5147,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
-      <c r="F15" s="32" t="s">
-        <v>266</v>
+      <c r="F15" s="31" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -5147,13 +5161,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
-      <c r="F16" s="32" t="s">
-        <v>268</v>
+      <c r="F16" s="31" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -5161,13 +5175,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
-      <c r="F17" s="32" t="s">
-        <v>270</v>
+      <c r="F17" s="31" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -5175,13 +5189,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
-      <c r="F18" s="32" t="s">
-        <v>272</v>
+      <c r="F18" s="31" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -5189,13 +5203,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
-      <c r="F19" s="32" t="s">
-        <v>274</v>
+      <c r="F19" s="31" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -5203,13 +5217,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
-      <c r="F20" s="32" t="s">
-        <v>276</v>
+      <c r="F20" s="31" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -5217,13 +5231,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
-      <c r="F21" s="32" t="s">
-        <v>278</v>
+      <c r="F21" s="31" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -5231,13 +5245,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
-      <c r="F22" s="32" t="s">
-        <v>280</v>
+      <c r="F22" s="31" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -5245,13 +5259,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
-      <c r="F23" s="32" t="s">
-        <v>282</v>
+      <c r="F23" s="31" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -5259,13 +5273,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
-      <c r="F24" s="32" t="s">
-        <v>284</v>
+      <c r="F24" s="31" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -5273,13 +5287,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
-      <c r="F25" s="32" t="s">
-        <v>286</v>
+      <c r="F25" s="31" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -5287,13 +5301,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
-      <c r="F26" s="32" t="s">
-        <v>288</v>
+      <c r="F26" s="31" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -5301,13 +5315,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
-      <c r="F27" s="32" t="s">
-        <v>290</v>
+      <c r="F27" s="31" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -5315,13 +5329,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
-      <c r="F28" s="32" t="s">
-        <v>292</v>
+      <c r="F28" s="31" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -5329,13 +5343,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
-      <c r="F29" s="32" t="s">
-        <v>294</v>
+      <c r="F29" s="31" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -5343,13 +5357,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>296</v>
+      <c r="F30" s="31" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -5357,13 +5371,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
-      <c r="F31" s="32" t="s">
-        <v>298</v>
+      <c r="F31" s="31" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -5371,13 +5385,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
-      <c r="F32" s="32" t="s">
-        <v>300</v>
+      <c r="F32" s="31" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -5385,13 +5399,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
-      <c r="F33" s="32" t="s">
-        <v>302</v>
+      <c r="F33" s="31" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -5399,13 +5413,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
-      <c r="F34" s="32" t="s">
-        <v>304</v>
+      <c r="F34" s="31" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -5413,13 +5427,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
-      <c r="F35" s="32" t="s">
-        <v>306</v>
+      <c r="F35" s="31" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -5427,13 +5441,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
-      <c r="F36" s="32" t="s">
-        <v>308</v>
+      <c r="F36" s="31" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -5441,13 +5455,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
-      <c r="F37" s="32" t="s">
-        <v>310</v>
+      <c r="F37" s="31" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -5455,13 +5469,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
-      <c r="F38" s="32" t="s">
-        <v>312</v>
+      <c r="F38" s="31" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -5469,13 +5483,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
-      <c r="F39" s="32" t="s">
-        <v>314</v>
+      <c r="F39" s="31" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -5483,13 +5497,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
-      <c r="F40" s="32" t="s">
-        <v>316</v>
+      <c r="F40" s="31" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -5497,13 +5511,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
-      <c r="F41" s="32" t="s">
-        <v>318</v>
+      <c r="F41" s="31" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -5511,13 +5525,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
-      <c r="F42" s="32" t="s">
-        <v>320</v>
+      <c r="F42" s="31" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -5525,13 +5539,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
-      <c r="F43" s="32" t="s">
-        <v>322</v>
+      <c r="F43" s="31" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -5539,13 +5553,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
-      <c r="F44" s="32" t="s">
-        <v>324</v>
+      <c r="F44" s="31" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -5553,13 +5567,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
-      <c r="F45" s="32" t="s">
-        <v>326</v>
+      <c r="F45" s="31" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -5567,13 +5581,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
-      <c r="F46" s="32" t="s">
-        <v>328</v>
+      <c r="F46" s="31" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -5581,13 +5595,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
-      <c r="F47" s="32" t="s">
-        <v>330</v>
+      <c r="F47" s="31" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -5595,13 +5609,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
-      <c r="F48" s="32" t="s">
-        <v>332</v>
+      <c r="F48" s="31" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -5609,13 +5623,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
-      <c r="F49" s="32" t="s">
-        <v>334</v>
+      <c r="F49" s="31" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -5623,13 +5637,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
-      <c r="F50" s="32" t="s">
-        <v>336</v>
+      <c r="F50" s="31" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -5637,13 +5651,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
-      <c r="F51" s="32" t="s">
-        <v>338</v>
+      <c r="F51" s="31" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -5651,13 +5665,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
-      <c r="F52" s="32" t="s">
-        <v>340</v>
+      <c r="F52" s="31" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -5665,13 +5679,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
-      <c r="F53" s="32" t="s">
-        <v>341</v>
+      <c r="F53" s="31" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -5679,13 +5693,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
-      <c r="F54" s="32" t="s">
-        <v>343</v>
+      <c r="F54" s="31" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -5693,13 +5707,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
-      <c r="F55" s="32" t="s">
-        <v>345</v>
+      <c r="F55" s="31" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -5707,13 +5721,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
-      <c r="F56" s="32" t="s">
-        <v>347</v>
+      <c r="F56" s="31" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -5721,13 +5735,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
-      <c r="F57" s="32" t="s">
-        <v>349</v>
+      <c r="F57" s="31" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -5735,13 +5749,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
-      <c r="F58" s="32" t="s">
-        <v>351</v>
+      <c r="F58" s="31" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -5749,13 +5763,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
-      <c r="F59" s="32" t="s">
-        <v>353</v>
+      <c r="F59" s="31" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -5763,13 +5777,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
-      <c r="F60" s="32" t="s">
-        <v>355</v>
+      <c r="F60" s="31" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -5777,13 +5791,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
-      <c r="F61" s="32" t="s">
-        <v>357</v>
+      <c r="F61" s="31" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -5791,13 +5805,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
-      <c r="F62" s="32" t="s">
-        <v>358</v>
+      <c r="F62" s="31" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -5805,13 +5819,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
-      <c r="F63" s="32" t="s">
-        <v>360</v>
+      <c r="F63" s="31" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -5819,13 +5833,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
-      <c r="F64" s="32" t="s">
-        <v>362</v>
+      <c r="F64" s="31" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -5833,13 +5847,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
-      <c r="F65" s="32" t="s">
-        <v>364</v>
+      <c r="F65" s="31" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -5847,13 +5861,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
-      <c r="F66" s="32" t="s">
-        <v>366</v>
+      <c r="F66" s="31" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -5861,13 +5875,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
-      <c r="F67" s="32" t="s">
-        <v>368</v>
+      <c r="F67" s="31" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -5875,13 +5889,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
-      <c r="F68" s="32" t="s">
-        <v>370</v>
+      <c r="F68" s="31" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -5889,13 +5903,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
-      <c r="F69" s="32" t="s">
-        <v>372</v>
+      <c r="F69" s="31" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -5903,13 +5917,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
-      <c r="F70" s="32" t="s">
-        <v>374</v>
+      <c r="F70" s="31" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -5917,13 +5931,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
-      <c r="F71" s="32" t="s">
-        <v>376</v>
+      <c r="F71" s="31" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -5931,13 +5945,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
-      <c r="F72" s="32" t="s">
-        <v>377</v>
+      <c r="F72" s="31" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -5945,13 +5959,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
-      <c r="F73" s="32" t="s">
-        <v>379</v>
+      <c r="F73" s="31" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -5959,13 +5973,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
-      <c r="F74" s="32" t="s">
-        <v>381</v>
+      <c r="F74" s="31" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5973,13 +5987,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
-      <c r="F75" s="32" t="s">
-        <v>383</v>
+      <c r="F75" s="31" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -5987,13 +6001,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
-      <c r="F76" s="32" t="s">
-        <v>385</v>
+      <c r="F76" s="31" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -6001,13 +6015,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
-      <c r="F77" s="32" t="s">
-        <v>387</v>
+      <c r="F77" s="31" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:6">
@@ -6015,13 +6029,13 @@
         <v>180073</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E78" s="6">
         <v>18</v>
       </c>
-      <c r="F78" s="32" t="s">
-        <v>389</v>
+      <c r="F78" s="31" t="s">
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -6103,13 +6117,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -6195,13 +6209,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="33" t="s">
-        <v>393</v>
+      <c r="F6" s="32" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6209,13 +6223,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>395</v>
+      <c r="F7" s="32" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6223,13 +6237,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F8" s="33" t="s">
-        <v>397</v>
+      <c r="F8" s="32" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6237,13 +6251,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="33" t="s">
-        <v>399</v>
+      <c r="F9" s="32" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6251,13 +6265,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
-      <c r="F10" s="33" t="s">
-        <v>401</v>
+      <c r="F10" s="32" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6265,13 +6279,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="33" t="s">
-        <v>403</v>
+      <c r="F11" s="32" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6279,13 +6293,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
-      <c r="F12" s="33" t="s">
-        <v>405</v>
+      <c r="F12" s="32" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6293,13 +6307,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
-      <c r="F13" s="34" t="s">
-        <v>407</v>
+      <c r="F13" s="33" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -6307,13 +6321,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
-      <c r="F14" s="34" t="s">
-        <v>409</v>
+      <c r="F14" s="33" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -6423,13 +6437,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
-      <c r="F6" s="32" t="s">
-        <v>411</v>
+      <c r="F6" s="31" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6437,13 +6451,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
-      <c r="F7" s="32" t="s">
-        <v>413</v>
+      <c r="F7" s="31" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6451,13 +6465,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
-      <c r="F8" s="32" t="s">
-        <v>415</v>
+      <c r="F8" s="31" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6465,13 +6479,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
-      <c r="F9" s="32" t="s">
-        <v>417</v>
+      <c r="F9" s="31" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6479,13 +6493,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
-      <c r="F10" s="32" t="s">
-        <v>419</v>
+      <c r="F10" s="31" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6493,13 +6507,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="32" t="s">
-        <v>421</v>
+      <c r="F11" s="31" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6507,13 +6521,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>423</v>
+      <c r="F12" s="31" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6521,13 +6535,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
-      <c r="F13" s="32" t="s">
-        <v>425</v>
+      <c r="F13" s="31" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6535,13 +6549,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
-      <c r="F14" s="32" t="s">
-        <v>427</v>
+      <c r="F14" s="31" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -6549,13 +6563,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
-      <c r="F15" s="32" t="s">
-        <v>429</v>
+      <c r="F15" s="31" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -6563,13 +6577,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
-      <c r="F16" s="32" t="s">
-        <v>431</v>
+      <c r="F16" s="31" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -6577,13 +6591,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
-      <c r="F17" s="32" t="s">
-        <v>433</v>
+      <c r="F17" s="31" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -6591,13 +6605,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
-      <c r="F18" s="32" t="s">
-        <v>435</v>
+      <c r="F18" s="31" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -6605,13 +6619,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
-      <c r="F19" s="32" t="s">
-        <v>437</v>
+      <c r="F19" s="31" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -6619,13 +6633,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
-      <c r="F20" s="32" t="s">
-        <v>439</v>
+      <c r="F20" s="31" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -6633,13 +6647,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
-      <c r="F21" s="32" t="s">
-        <v>441</v>
+      <c r="F21" s="31" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -6647,13 +6661,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
-      <c r="F22" s="32" t="s">
-        <v>443</v>
+      <c r="F22" s="31" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -6661,13 +6675,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
-      <c r="F23" s="32" t="s">
-        <v>445</v>
+      <c r="F23" s="31" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6675,13 +6689,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
-      <c r="F24" s="32" t="s">
-        <v>447</v>
+      <c r="F24" s="31" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6689,13 +6703,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
-      <c r="F25" s="32" t="s">
-        <v>449</v>
+      <c r="F25" s="31" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6703,13 +6717,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
-      <c r="F26" s="32" t="s">
-        <v>451</v>
+      <c r="F26" s="31" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6717,13 +6731,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
-      <c r="F27" s="32" t="s">
-        <v>453</v>
+      <c r="F27" s="31" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6731,13 +6745,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
-      <c r="F28" s="32" t="s">
-        <v>455</v>
+      <c r="F28" s="31" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6745,13 +6759,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
-      <c r="F29" s="32" t="s">
-        <v>457</v>
+      <c r="F29" s="31" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6759,13 +6773,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>459</v>
+      <c r="F30" s="31" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6773,13 +6787,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
-      <c r="F31" s="32" t="s">
-        <v>461</v>
+      <c r="F31" s="31" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6787,13 +6801,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
-      <c r="F32" s="32" t="s">
-        <v>463</v>
+      <c r="F32" s="31" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -6801,13 +6815,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
-      <c r="F33" s="32" t="s">
-        <v>465</v>
+      <c r="F33" s="31" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -6815,13 +6829,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
-      <c r="F34" s="32" t="s">
-        <v>467</v>
+      <c r="F34" s="31" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -6829,13 +6843,13 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
-      <c r="F35" s="32" t="s">
-        <v>469</v>
+      <c r="F35" s="31" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -6843,13 +6857,13 @@
         <v>50031</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
       </c>
-      <c r="F36" s="32" t="s">
-        <v>471</v>
+      <c r="F36" s="31" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -6857,13 +6871,13 @@
         <v>50032</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
       </c>
-      <c r="F37" s="32" t="s">
-        <v>473</v>
+      <c r="F37" s="31" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -6871,13 +6885,13 @@
         <v>50033</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
       </c>
-      <c r="F38" s="32" t="s">
-        <v>475</v>
+      <c r="F38" s="31" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -6885,13 +6899,13 @@
         <v>50034</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
       </c>
-      <c r="F39" s="32" t="s">
-        <v>477</v>
+      <c r="F39" s="31" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -6899,13 +6913,13 @@
         <v>50035</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
       </c>
-      <c r="F40" s="32" t="s">
-        <v>479</v>
+      <c r="F40" s="31" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -6913,13 +6927,13 @@
         <v>50036</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
       </c>
-      <c r="F41" s="32" t="s">
-        <v>481</v>
+      <c r="F41" s="31" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -6927,13 +6941,13 @@
         <v>50037</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E42" s="1">
         <v>6</v>
       </c>
-      <c r="F42" s="31" t="s">
-        <v>483</v>
+      <c r="F42" s="30" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -6941,13 +6955,13 @@
         <v>50038</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E43" s="1">
         <v>6</v>
       </c>
-      <c r="F43" s="31" t="s">
-        <v>484</v>
+      <c r="F43" s="30" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -6955,13 +6969,13 @@
         <v>50039</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E44" s="1">
         <v>6</v>
       </c>
-      <c r="F44" s="31" t="s">
-        <v>485</v>
+      <c r="F44" s="30" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -6969,13 +6983,13 @@
         <v>50040</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E45" s="1">
         <v>6</v>
       </c>
-      <c r="F45" s="31" t="s">
-        <v>486</v>
+      <c r="F45" s="30" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -6983,13 +6997,13 @@
         <v>50041</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E46" s="1">
         <v>6</v>
       </c>
-      <c r="F46" s="31" t="s">
-        <v>487</v>
+      <c r="F46" s="30" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -6997,13 +7011,13 @@
         <v>50042</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E47" s="1">
         <v>6</v>
       </c>
-      <c r="F47" s="31" t="s">
-        <v>488</v>
+      <c r="F47" s="30" t="s">
+        <v>490</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="493">
   <si>
     <t>_id</t>
   </si>
@@ -560,7 +560,13 @@
     <t>凤凰之羽</t>
   </si>
   <si>
-    <t>5008</t>
+    <t>8301</t>
+  </si>
+  <si>
+    <t>翅膀部件</t>
+  </si>
+  <si>
+    <t>8302,8303,8304,8305,8306,8307</t>
   </si>
   <si>
     <t>魂环1</t>
@@ -3309,18 +3315,32 @@
         <v>44</v>
       </c>
     </row>
+    <row r="23" customHeight="1" spans="3:6">
+      <c r="C23" s="19">
+        <v>18</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="19">
+        <v>5</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="26" customHeight="1" spans="3:6">
       <c r="C26" s="19">
         <v>21</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E26" s="19">
         <v>5</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -3328,13 +3348,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E27" s="19">
         <v>5</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -3342,13 +3362,13 @@
         <v>23</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E28" s="19">
         <v>5</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -3356,13 +3376,13 @@
         <v>24</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E29" s="19">
         <v>5</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -3370,13 +3390,13 @@
         <v>25</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E30" s="19">
         <v>5</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -3384,13 +3404,13 @@
         <v>26</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E31" s="19">
         <v>5</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -3398,13 +3418,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E32" s="19">
         <v>5</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -3412,13 +3432,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E33" s="19">
         <v>5</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -3426,13 +3446,13 @@
         <v>29</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E34" s="19">
         <v>5</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -3508,13 +3528,13 @@
         <v>20001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -3522,13 +3542,13 @@
         <v>20002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -3536,13 +3556,13 @@
         <v>20003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -3550,13 +3570,13 @@
         <v>20004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -3564,13 +3584,13 @@
         <v>20005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -3578,13 +3598,13 @@
         <v>20006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -3592,13 +3612,13 @@
         <v>20007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -3606,13 +3626,13 @@
         <v>20008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -3620,13 +3640,13 @@
         <v>20009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -3634,13 +3654,13 @@
         <v>20010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -3648,13 +3668,13 @@
         <v>20011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -3662,13 +3682,13 @@
         <v>20012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -3676,13 +3696,13 @@
         <v>20013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -3690,13 +3710,13 @@
         <v>20014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -3704,13 +3724,13 @@
         <v>20015</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -3718,13 +3738,13 @@
         <v>20016</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -3732,13 +3752,13 @@
         <v>20017</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -3746,13 +3766,13 @@
         <v>20018</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -3760,13 +3780,13 @@
         <v>20019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -3774,13 +3794,13 @@
         <v>20020</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -3788,13 +3808,13 @@
         <v>20021</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -3802,13 +3822,13 @@
         <v>20022</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -3816,13 +3836,13 @@
         <v>20023</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -3830,13 +3850,13 @@
         <v>20024</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -3844,13 +3864,13 @@
         <v>20025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -3858,13 +3878,13 @@
         <v>20026</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -3872,13 +3892,13 @@
         <v>20027</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="F32" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -3886,13 +3906,13 @@
         <v>20028</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -3900,13 +3920,13 @@
         <v>20029</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -3914,13 +3934,13 @@
         <v>20030</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -3928,13 +3948,13 @@
         <v>20031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -3942,13 +3962,13 @@
         <v>20032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -3956,13 +3976,13 @@
         <v>20033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -3970,13 +3990,13 @@
         <v>20034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -3984,13 +4004,13 @@
         <v>20035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -3998,13 +4018,13 @@
         <v>20036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -4012,13 +4032,13 @@
         <v>20037</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
       <c r="F42" s="29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -4026,13 +4046,13 @@
         <v>20038</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -4040,13 +4060,13 @@
         <v>20039</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -4054,13 +4074,13 @@
         <v>20040</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -4068,13 +4088,13 @@
         <v>20041</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -4082,13 +4102,13 @@
         <v>20042</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -4096,13 +4116,13 @@
         <v>20043</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -4110,13 +4130,13 @@
         <v>20044</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -4124,13 +4144,13 @@
         <v>20045</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -4138,13 +4158,13 @@
         <v>20046</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -4152,13 +4172,13 @@
         <v>20047</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -4166,13 +4186,13 @@
         <v>20048</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -4180,13 +4200,13 @@
         <v>20049</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -4194,13 +4214,13 @@
         <v>20050</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -4208,13 +4228,13 @@
         <v>20051</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -4222,13 +4242,13 @@
         <v>20052</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -4236,13 +4256,13 @@
         <v>20053</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -4250,13 +4270,13 @@
         <v>20054</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -4264,13 +4284,13 @@
         <v>20055</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -4278,13 +4298,13 @@
         <v>20056</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -4292,13 +4312,13 @@
         <v>20057</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
       <c r="F62" s="30" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -4306,13 +4326,13 @@
         <v>20058</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
       <c r="F63" s="30" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -4320,13 +4340,13 @@
         <v>20059</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
       <c r="F64" s="30" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -4334,13 +4354,13 @@
         <v>20060</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="F65" s="30" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -4348,13 +4368,13 @@
         <v>20061</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -4362,13 +4382,13 @@
         <v>20062</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -4376,13 +4396,13 @@
         <v>20063</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -4390,13 +4410,13 @@
         <v>20064</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -4404,13 +4424,13 @@
         <v>20065</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -4418,13 +4438,13 @@
         <v>20066</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="F71" s="30" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -4432,13 +4452,13 @@
         <v>20067</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
       <c r="F72" s="30" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -4446,13 +4466,13 @@
         <v>20068</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
       <c r="F73" s="30" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -4460,13 +4480,13 @@
         <v>20069</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
       <c r="F74" s="30" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -4474,13 +4494,13 @@
         <v>20070</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
       <c r="F75" s="30" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -4488,13 +4508,13 @@
         <v>20071</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
       </c>
       <c r="F76" s="30" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -4502,13 +4522,13 @@
         <v>20072</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
       </c>
       <c r="F77" s="30" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:6">
@@ -4516,13 +4536,13 @@
         <v>20073</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
       </c>
       <c r="F78" s="30" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:6">
@@ -4530,13 +4550,13 @@
         <v>20074</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
       </c>
       <c r="F79" s="30" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:6">
@@ -4544,13 +4564,13 @@
         <v>20075</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
       </c>
       <c r="F80" s="30" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:6">
@@ -4558,13 +4578,13 @@
         <v>20076</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
       </c>
       <c r="F81" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:6">
@@ -4572,13 +4592,13 @@
         <v>20077</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
       </c>
       <c r="F82" s="30" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:6">
@@ -4586,13 +4606,13 @@
         <v>20078</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:6">
@@ -4672,13 +4692,13 @@
         <v>21001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4686,13 +4706,13 @@
         <v>21002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4700,13 +4720,13 @@
         <v>21003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4714,13 +4734,13 @@
         <v>21004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4728,13 +4748,13 @@
         <v>21005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4742,13 +4762,13 @@
         <v>21006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4756,13 +4776,13 @@
         <v>21007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4770,13 +4790,13 @@
         <v>21008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4784,13 +4804,13 @@
         <v>21009</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4798,13 +4818,13 @@
         <v>21010</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4812,13 +4832,13 @@
         <v>21011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4826,13 +4846,13 @@
         <v>21012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4840,13 +4860,13 @@
         <v>21013</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4854,13 +4874,13 @@
         <v>21014</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4868,13 +4888,13 @@
         <v>21015</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5021,13 +5041,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -5035,13 +5055,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -5049,13 +5069,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -5063,13 +5083,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -5077,13 +5097,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -5091,13 +5111,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -5105,13 +5125,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -5119,13 +5139,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -5133,13 +5153,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -5147,13 +5167,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -5161,13 +5181,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -5175,13 +5195,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -5189,13 +5209,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -5203,13 +5223,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -5217,13 +5237,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -5231,13 +5251,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -5245,13 +5265,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -5259,13 +5279,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -5273,13 +5293,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -5287,13 +5307,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -5301,13 +5321,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -5315,13 +5335,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -5329,13 +5349,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -5343,13 +5363,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -5357,13 +5377,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -5371,13 +5391,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -5385,13 +5405,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -5399,13 +5419,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -5413,13 +5433,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -5427,13 +5447,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -5441,13 +5461,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -5455,13 +5475,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -5469,13 +5489,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -5483,13 +5503,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -5497,13 +5517,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -5511,13 +5531,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -5525,13 +5545,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -5539,13 +5559,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -5553,13 +5573,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -5567,13 +5587,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -5581,13 +5601,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -5595,13 +5615,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -5609,13 +5629,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -5623,13 +5643,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -5637,13 +5657,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
       <c r="F50" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -5651,13 +5671,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
       <c r="F51" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -5665,13 +5685,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -5679,13 +5699,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
       <c r="F53" s="31" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -5693,13 +5713,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -5707,13 +5727,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
       <c r="F55" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -5721,13 +5741,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
       <c r="F56" s="31" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -5735,13 +5755,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
       <c r="F57" s="31" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -5749,13 +5769,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
       <c r="F58" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -5763,13 +5783,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
       <c r="F59" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -5777,13 +5797,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
       <c r="F60" s="31" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -5791,13 +5811,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
       <c r="F61" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -5805,13 +5825,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -5819,13 +5839,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
       <c r="F63" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -5833,13 +5853,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
       <c r="F64" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -5847,13 +5867,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
       <c r="F65" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -5861,13 +5881,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
       <c r="F66" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -5875,13 +5895,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
       <c r="F67" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -5889,13 +5909,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -5903,13 +5923,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
       <c r="F69" s="31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -5917,13 +5937,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
       <c r="F70" s="31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -5931,13 +5951,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
       <c r="F71" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -5945,13 +5965,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
       <c r="F72" s="31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -5959,13 +5979,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
       <c r="F73" s="31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -5973,13 +5993,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
       <c r="F74" s="31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5987,13 +6007,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
       <c r="F75" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -6001,13 +6021,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
       <c r="F76" s="31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -6015,13 +6035,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
       <c r="F77" s="31" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:6">
@@ -6029,13 +6049,13 @@
         <v>180073</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E78" s="6">
         <v>18</v>
       </c>
       <c r="F78" s="31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -6117,13 +6137,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -6209,13 +6229,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6223,13 +6243,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6237,13 +6257,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6251,13 +6271,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6265,13 +6285,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6279,13 +6299,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6293,13 +6313,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6307,13 +6327,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -6321,13 +6341,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -6437,13 +6457,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6451,13 +6471,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6465,13 +6485,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6479,13 +6499,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6493,13 +6513,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6507,13 +6527,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6521,13 +6541,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6535,13 +6555,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6549,13 +6569,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -6563,13 +6583,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -6577,13 +6597,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -6591,13 +6611,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -6605,13 +6625,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -6619,13 +6639,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -6633,13 +6653,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -6647,13 +6667,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -6661,13 +6681,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -6675,13 +6695,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6689,13 +6709,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6703,13 +6723,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6717,13 +6737,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6731,13 +6751,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6745,13 +6765,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6759,13 +6779,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6773,13 +6793,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6787,13 +6807,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6801,13 +6821,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -6815,13 +6835,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -6829,13 +6849,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -6843,13 +6863,13 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -6857,13 +6877,13 @@
         <v>50031</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -6871,13 +6891,13 @@
         <v>50032</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -6885,13 +6905,13 @@
         <v>50033</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -6899,13 +6919,13 @@
         <v>50034</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -6913,13 +6933,13 @@
         <v>50035</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -6927,13 +6947,13 @@
         <v>50036</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -6941,13 +6961,13 @@
         <v>50037</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E42" s="1">
         <v>6</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -6955,13 +6975,13 @@
         <v>50038</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E43" s="1">
         <v>6</v>
       </c>
       <c r="F43" s="30" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -6969,13 +6989,13 @@
         <v>50039</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E44" s="1">
         <v>6</v>
       </c>
       <c r="F44" s="30" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -6983,13 +7003,13 @@
         <v>50040</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E45" s="1">
         <v>6</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -6997,13 +7017,13 @@
         <v>50041</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E46" s="1">
         <v>6</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -7011,13 +7031,13 @@
         <v>50042</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E47" s="1">
         <v>6</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
